--- a/dashboards/NJ.xlsx
+++ b/dashboards/NJ.xlsx
@@ -479,7 +479,7 @@
         <v>2164.573486328125</v>
       </c>
       <c r="C2" t="n">
-        <v>214.1918029785156</v>
+        <v>214.1918182373047</v>
       </c>
       <c r="D2" t="n">
         <v>5506.39990234375</v>
@@ -494,10 +494,10 @@
         <v>1845.327270507812</v>
       </c>
       <c r="H2" t="n">
-        <v>800.53662109375</v>
+        <v>800.5365600585938</v>
       </c>
       <c r="I2" t="n">
-        <v>1049.6943359375</v>
+        <v>1049.694580078125</v>
       </c>
     </row>
     <row r="3">
@@ -523,10 +523,10 @@
         <v>1859.434814453125</v>
       </c>
       <c r="H3" t="n">
-        <v>802.5142822265625</v>
+        <v>802.5143432617188</v>
       </c>
       <c r="I3" t="n">
-        <v>1051.038208007812</v>
+        <v>1051.0380859375</v>
       </c>
     </row>
     <row r="4">
@@ -534,10 +534,10 @@
         <v>44566</v>
       </c>
       <c r="B4" t="n">
-        <v>2154.91064453125</v>
+        <v>2154.910888671875</v>
       </c>
       <c r="C4" t="n">
-        <v>210.8586730957031</v>
+        <v>210.8586578369141</v>
       </c>
       <c r="D4" t="n">
         <v>5302.64599609375</v>
@@ -552,10 +552,10 @@
         <v>1870.039184570312</v>
       </c>
       <c r="H4" t="n">
-        <v>809.8944702148438</v>
+        <v>809.89453125</v>
       </c>
       <c r="I4" t="n">
-        <v>1065.868774414062</v>
+        <v>1065.869018554688</v>
       </c>
     </row>
     <row r="5">
@@ -563,10 +563,10 @@
         <v>44567</v>
       </c>
       <c r="B5" t="n">
-        <v>2141.45068359375</v>
+        <v>2141.450439453125</v>
       </c>
       <c r="C5" t="n">
-        <v>210.5205078125</v>
+        <v>210.5205230712891</v>
       </c>
       <c r="D5" t="n">
         <v>5328.14599609375</v>
@@ -584,7 +584,7 @@
         <v>810.232177734375</v>
       </c>
       <c r="I5" t="n">
-        <v>1075.32470703125</v>
+        <v>1075.324829101562</v>
       </c>
     </row>
     <row r="6">
@@ -592,10 +592,10 @@
         <v>44568</v>
       </c>
       <c r="B6" t="n">
-        <v>2196.5419921875</v>
+        <v>2196.542236328125</v>
       </c>
       <c r="C6" t="n">
-        <v>214.0951995849609</v>
+        <v>214.09521484375</v>
       </c>
       <c r="D6" t="n">
         <v>5284.77978515625</v>
@@ -607,13 +607,13 @@
         <v>129.25</v>
       </c>
       <c r="G6" t="n">
-        <v>1828.10107421875</v>
+        <v>1828.100952148438</v>
       </c>
       <c r="H6" t="n">
         <v>799.7648315429688</v>
       </c>
       <c r="I6" t="n">
-        <v>1080.152099609375</v>
+        <v>1080.151977539062</v>
       </c>
     </row>
     <row r="7">
@@ -624,7 +624,7 @@
         <v>2230.721435546875</v>
       </c>
       <c r="C7" t="n">
-        <v>219.1674346923828</v>
+        <v>219.1674194335938</v>
       </c>
       <c r="D7" t="n">
         <v>5279.93994140625</v>
@@ -636,13 +636,13 @@
         <v>130.1999969482422</v>
       </c>
       <c r="G7" t="n">
-        <v>1874.357666015625</v>
+        <v>1874.357788085938</v>
       </c>
       <c r="H7" t="n">
-        <v>812.258056640625</v>
+        <v>812.2581176757812</v>
       </c>
       <c r="I7" t="n">
-        <v>1067.013427734375</v>
+        <v>1067.013549804688</v>
       </c>
     </row>
     <row r="8">
@@ -671,7 +671,7 @@
         <v>811.7275390625</v>
       </c>
       <c r="I8" t="n">
-        <v>1113.944213867188</v>
+        <v>1113.944091796875</v>
       </c>
     </row>
     <row r="9">
@@ -679,7 +679,7 @@
         <v>44573</v>
       </c>
       <c r="B9" t="n">
-        <v>2225.577880859375</v>
+        <v>2225.57763671875</v>
       </c>
       <c r="C9" t="n">
         <v>226.510009765625</v>
@@ -711,7 +711,7 @@
         <v>2224.952880859375</v>
       </c>
       <c r="C10" t="n">
-        <v>225.8820495605469</v>
+        <v>225.8820343017578</v>
       </c>
       <c r="D10" t="n">
         <v>5259.22998046875</v>
@@ -723,13 +723,13 @@
         <v>133.1000061035156</v>
       </c>
       <c r="G10" t="n">
-        <v>1937.025268554688</v>
+        <v>1937.025146484375</v>
       </c>
       <c r="H10" t="n">
         <v>864.402099609375</v>
       </c>
       <c r="I10" t="n">
-        <v>1177.397583007812</v>
+        <v>1177.397827148438</v>
       </c>
     </row>
     <row r="11">
@@ -752,13 +752,13 @@
         <v>133.6000061035156</v>
       </c>
       <c r="G11" t="n">
-        <v>1962.312744140625</v>
+        <v>1962.312866210938</v>
       </c>
       <c r="H11" t="n">
-        <v>850.1239624023438</v>
+        <v>850.1239013671875</v>
       </c>
       <c r="I11" t="n">
-        <v>1159.431762695312</v>
+        <v>1159.431640625</v>
       </c>
     </row>
     <row r="12">
@@ -766,7 +766,7 @@
         <v>44578</v>
       </c>
       <c r="B12" t="n">
-        <v>2286.966796875</v>
+        <v>2286.966552734375</v>
       </c>
       <c r="C12" t="n">
         <v>259.3102416992188</v>
@@ -787,7 +787,7 @@
         <v>869.03271484375</v>
       </c>
       <c r="I12" t="n">
-        <v>1152.862426757812</v>
+        <v>1152.862548828125</v>
       </c>
     </row>
     <row r="13">
@@ -810,10 +810,10 @@
         <v>133.0500030517578</v>
       </c>
       <c r="G13" t="n">
-        <v>1940.671875</v>
+        <v>1940.671997070312</v>
       </c>
       <c r="H13" t="n">
-        <v>860.6878662109375</v>
+        <v>860.6878051757812</v>
       </c>
       <c r="I13" t="n">
         <v>1138.977294921875</v>
@@ -824,7 +824,7 @@
         <v>44580</v>
       </c>
       <c r="B14" t="n">
-        <v>2145.777099609375</v>
+        <v>2145.77685546875</v>
       </c>
       <c r="C14" t="n">
         <v>309.5975341796875</v>
@@ -839,10 +839,10 @@
         <v>129.1999969482422</v>
       </c>
       <c r="G14" t="n">
-        <v>1939.42431640625</v>
+        <v>1939.424438476562</v>
       </c>
       <c r="H14" t="n">
-        <v>862.8585205078125</v>
+        <v>862.8584594726562</v>
       </c>
       <c r="I14" t="n">
         <v>1162.119140625</v>
@@ -885,7 +885,7 @@
         <v>2130.345458984375</v>
       </c>
       <c r="C16" t="n">
-        <v>307.3270874023438</v>
+        <v>307.3271179199219</v>
       </c>
       <c r="D16" t="n">
         <v>4969.5927734375</v>
@@ -900,7 +900,7 @@
         <v>1877.18896484375</v>
       </c>
       <c r="H16" t="n">
-        <v>844.3356323242188</v>
+        <v>844.3355712890625</v>
       </c>
       <c r="I16" t="n">
         <v>1176.3525390625</v>
@@ -914,10 +914,10 @@
         <v>2083.906982421875</v>
       </c>
       <c r="C17" t="n">
-        <v>309.0178527832031</v>
+        <v>309.0178833007812</v>
       </c>
       <c r="D17" t="n">
-        <v>4611.58837890625</v>
+        <v>4611.5888671875</v>
       </c>
       <c r="E17" t="n">
         <v>4035.300048828125</v>
@@ -932,7 +932,7 @@
         <v>824.5584716796875</v>
       </c>
       <c r="I17" t="n">
-        <v>1116.731079101562</v>
+        <v>1116.731323242188</v>
       </c>
     </row>
     <row r="18">
@@ -946,7 +946,7 @@
         <v>303.2210388183594</v>
       </c>
       <c r="D18" t="n">
-        <v>4543.27099609375</v>
+        <v>4543.271484375</v>
       </c>
       <c r="E18" t="n">
         <v>4095.449951171875</v>
@@ -958,7 +958,7 @@
         <v>1847.6787109375</v>
       </c>
       <c r="H18" t="n">
-        <v>824.3656005859375</v>
+        <v>824.3655395507812</v>
       </c>
       <c r="I18" t="n">
         <v>1074.329467773438</v>
@@ -990,7 +990,7 @@
         <v>827.7903442382812</v>
       </c>
       <c r="I19" t="n">
-        <v>1018.191711425781</v>
+        <v>1018.191772460938</v>
       </c>
     </row>
     <row r="20">
@@ -1001,10 +1001,10 @@
         <v>2130.537841796875</v>
       </c>
       <c r="C20" t="n">
-        <v>292.6901550292969</v>
+        <v>292.690185546875</v>
       </c>
       <c r="D20" t="n">
-        <v>4383.4814453125</v>
+        <v>4383.48193359375</v>
       </c>
       <c r="E20" t="n">
         <v>4076</v>
@@ -1016,7 +1016,7 @@
         <v>1821.04736328125</v>
       </c>
       <c r="H20" t="n">
-        <v>838.9813232421875</v>
+        <v>838.9812622070312</v>
       </c>
       <c r="I20" t="n">
         <v>1013.563354492188</v>
@@ -1033,7 +1033,7 @@
         <v>297.7140808105469</v>
       </c>
       <c r="D21" t="n">
-        <v>4398.7021484375</v>
+        <v>4398.70263671875</v>
       </c>
       <c r="E21" t="n">
         <v>4114.35009765625</v>
@@ -1045,7 +1045,7 @@
         <v>1832.227661132812</v>
       </c>
       <c r="H21" t="n">
-        <v>854.561767578125</v>
+        <v>854.5617065429688</v>
       </c>
       <c r="I21" t="n">
         <v>1026.751831054688</v>
@@ -1062,7 +1062,7 @@
         <v>305.7812805175781</v>
       </c>
       <c r="D22" t="n">
-        <v>4429.19287109375</v>
+        <v>4429.1923828125</v>
       </c>
       <c r="E22" t="n">
         <v>4225.60009765625</v>
@@ -1085,13 +1085,13 @@
         <v>44594</v>
       </c>
       <c r="B23" t="n">
-        <v>2217.64599609375</v>
+        <v>2217.645751953125</v>
       </c>
       <c r="C23" t="n">
-        <v>335.9246520996094</v>
+        <v>335.9246826171875</v>
       </c>
       <c r="D23" t="n">
-        <v>4619.42333984375</v>
+        <v>4619.4228515625</v>
       </c>
       <c r="E23" t="n">
         <v>4236.64990234375</v>
@@ -1100,10 +1100,10 @@
         <v>98.90000152587891</v>
       </c>
       <c r="G23" t="n">
-        <v>1902.764404296875</v>
+        <v>1902.764526367188</v>
       </c>
       <c r="H23" t="n">
-        <v>838.6917724609375</v>
+        <v>838.6918334960938</v>
       </c>
       <c r="I23" t="n">
         <v>1092.44482421875</v>
@@ -1117,10 +1117,10 @@
         <v>2205.195068359375</v>
       </c>
       <c r="C24" t="n">
-        <v>320.9496154785156</v>
+        <v>320.9495849609375</v>
       </c>
       <c r="D24" t="n">
-        <v>4516.2734375</v>
+        <v>4516.27294921875</v>
       </c>
       <c r="E24" t="n">
         <v>4140</v>
@@ -1129,13 +1129,13 @@
         <v>97.09999847412109</v>
       </c>
       <c r="G24" t="n">
-        <v>1855.69189453125</v>
+        <v>1855.692016601562</v>
       </c>
       <c r="H24" t="n">
-        <v>826.0056762695312</v>
+        <v>826.005615234375</v>
       </c>
       <c r="I24" t="n">
-        <v>1078.260986328125</v>
+        <v>1078.261108398438</v>
       </c>
     </row>
     <row r="25">
@@ -1143,10 +1143,10 @@
         <v>44596</v>
       </c>
       <c r="B25" t="n">
-        <v>2187.0712890625</v>
+        <v>2187.071533203125</v>
       </c>
       <c r="C25" t="n">
-        <v>321.4326477050781</v>
+        <v>321.4326782226562</v>
       </c>
       <c r="D25" t="n">
         <v>4483.83642578125</v>
@@ -1158,7 +1158,7 @@
         <v>94.19999694824219</v>
       </c>
       <c r="G25" t="n">
-        <v>1869.41552734375</v>
+        <v>1869.415405273438</v>
       </c>
       <c r="H25" t="n">
         <v>812.0169677734375</v>
@@ -1178,7 +1178,7 @@
         <v>318.3893127441406</v>
       </c>
       <c r="D26" t="n">
-        <v>4388.7216796875</v>
+        <v>4388.72119140625</v>
       </c>
       <c r="E26" t="n">
         <v>4073.550048828125</v>
@@ -1187,10 +1187,10 @@
         <v>93.55000305175781</v>
       </c>
       <c r="G26" t="n">
-        <v>1808.523559570312</v>
+        <v>1808.5234375</v>
       </c>
       <c r="H26" t="n">
-        <v>800.2471313476562</v>
+        <v>800.2471923828125</v>
       </c>
       <c r="I26" t="n">
         <v>1045.563720703125</v>
@@ -1201,7 +1201,7 @@
         <v>44600</v>
       </c>
       <c r="B27" t="n">
-        <v>2215.9150390625</v>
+        <v>2215.915283203125</v>
       </c>
       <c r="C27" t="n">
         <v>309.8390808105469</v>
@@ -1216,13 +1216,13 @@
         <v>93.55000305175781</v>
       </c>
       <c r="G27" t="n">
-        <v>1799.982421875</v>
+        <v>1799.982299804688</v>
       </c>
       <c r="H27" t="n">
         <v>802.707275390625</v>
       </c>
       <c r="I27" t="n">
-        <v>1049.047485351562</v>
+        <v>1049.047607421875</v>
       </c>
     </row>
     <row r="28">
@@ -1236,7 +1236,7 @@
         <v>312.3992919921875</v>
       </c>
       <c r="D28" t="n">
-        <v>4476.30078125</v>
+        <v>4476.30126953125</v>
       </c>
       <c r="E28" t="n">
         <v>4002.10009765625</v>
@@ -1248,7 +1248,7 @@
         <v>1812.650146484375</v>
       </c>
       <c r="H28" t="n">
-        <v>810.5699462890625</v>
+        <v>810.5698852539062</v>
       </c>
       <c r="I28" t="n">
         <v>1065.6201171875</v>
@@ -1259,10 +1259,10 @@
         <v>44602</v>
       </c>
       <c r="B29" t="n">
-        <v>2214.761474609375</v>
+        <v>2214.76171875</v>
       </c>
       <c r="C29" t="n">
-        <v>318.1478271484375</v>
+        <v>318.1477966308594</v>
       </c>
       <c r="D29" t="n">
         <v>4490.8232421875</v>
@@ -1274,13 +1274,13 @@
         <v>94.44999694824219</v>
       </c>
       <c r="G29" t="n">
-        <v>1824.358154296875</v>
+        <v>1824.358276367188</v>
       </c>
       <c r="H29" t="n">
-        <v>822.9666748046875</v>
+        <v>822.9667358398438</v>
       </c>
       <c r="I29" t="n">
-        <v>1070.596801757812</v>
+        <v>1070.5966796875</v>
       </c>
     </row>
     <row r="30">
@@ -1288,13 +1288,13 @@
         <v>44603</v>
       </c>
       <c r="B30" t="n">
-        <v>2162.650634765625</v>
+        <v>2162.65087890625</v>
       </c>
       <c r="C30" t="n">
         <v>304.38037109375</v>
       </c>
       <c r="D30" t="n">
-        <v>4356.08544921875</v>
+        <v>4356.0849609375</v>
       </c>
       <c r="E30" t="n">
         <v>4142.25</v>
@@ -1306,10 +1306,10 @@
         <v>1795.807739257812</v>
       </c>
       <c r="H30" t="n">
-        <v>823.5455932617188</v>
+        <v>823.5455322265625</v>
       </c>
       <c r="I30" t="n">
-        <v>1066.366577148438</v>
+        <v>1066.366455078125</v>
       </c>
     </row>
     <row r="31">
@@ -1323,7 +1323,7 @@
         <v>283.5119018554688</v>
       </c>
       <c r="D31" t="n">
-        <v>4138.45751953125</v>
+        <v>4138.45703125</v>
       </c>
       <c r="E31" t="n">
         <v>3979.75</v>
@@ -1335,10 +1335,10 @@
         <v>1726.470581054688</v>
       </c>
       <c r="H31" t="n">
-        <v>795.9541015625</v>
+        <v>795.9541625976562</v>
       </c>
       <c r="I31" t="n">
-        <v>1031.479858398438</v>
+        <v>1031.479614257812</v>
       </c>
     </row>
     <row r="32">
@@ -1352,7 +1352,7 @@
         <v>296.941162109375</v>
       </c>
       <c r="D32" t="n">
-        <v>4289.6142578125</v>
+        <v>4289.61474609375</v>
       </c>
       <c r="E32" t="n">
         <v>4081.75</v>
@@ -1367,7 +1367,7 @@
         <v>824.4619750976562</v>
       </c>
       <c r="I32" t="n">
-        <v>1076.56884765625</v>
+        <v>1076.568969726562</v>
       </c>
     </row>
     <row r="33">
@@ -1375,7 +1375,7 @@
         <v>44608</v>
       </c>
       <c r="B33" t="n">
-        <v>2153.084228515625</v>
+        <v>2153.083984375</v>
       </c>
       <c r="C33" t="n">
         <v>291.0477905273438</v>
@@ -1390,7 +1390,7 @@
         <v>84.94999694824219</v>
       </c>
       <c r="G33" t="n">
-        <v>1785.68310546875</v>
+        <v>1785.682983398438</v>
       </c>
       <c r="H33" t="n">
         <v>833.771728515625</v>
@@ -1410,7 +1410,7 @@
         <v>296.6996154785156</v>
       </c>
       <c r="D34" t="n">
-        <v>4185.3671875</v>
+        <v>4185.36669921875</v>
       </c>
       <c r="E34" t="n">
         <v>4115.39990234375</v>
@@ -1425,7 +1425,7 @@
         <v>831.8422241210938</v>
       </c>
       <c r="I34" t="n">
-        <v>1057.856323242188</v>
+        <v>1057.8564453125</v>
       </c>
     </row>
     <row r="35">
@@ -1436,7 +1436,7 @@
         <v>2097.0791015625</v>
       </c>
       <c r="C35" t="n">
-        <v>292.35205078125</v>
+        <v>292.3520202636719</v>
       </c>
       <c r="D35" t="n">
         <v>4061.70703125</v>
@@ -1465,10 +1465,10 @@
         <v>2100.6845703125</v>
       </c>
       <c r="C36" t="n">
-        <v>287.666259765625</v>
+        <v>287.6662902832031</v>
       </c>
       <c r="D36" t="n">
-        <v>4078.87353515625</v>
+        <v>4078.873779296875</v>
       </c>
       <c r="E36" t="n">
         <v>4096.60009765625</v>
@@ -1483,7 +1483,7 @@
         <v>811.4380493164062</v>
       </c>
       <c r="I36" t="n">
-        <v>1030.534057617188</v>
+        <v>1030.533935546875</v>
       </c>
     </row>
     <row r="37">
@@ -1512,7 +1512,7 @@
         <v>823.1596069335938</v>
       </c>
       <c r="I37" t="n">
-        <v>1045.273803710938</v>
+        <v>1045.27392578125</v>
       </c>
     </row>
     <row r="38">
@@ -1535,13 +1535,13 @@
         <v>84.15000152587891</v>
       </c>
       <c r="G38" t="n">
-        <v>1746.911865234375</v>
+        <v>1746.911987304688</v>
       </c>
       <c r="H38" t="n">
-        <v>820.3136596679688</v>
+        <v>820.3135986328125</v>
       </c>
       <c r="I38" t="n">
-        <v>1050.00439453125</v>
+        <v>1050.004516601562</v>
       </c>
     </row>
     <row r="39">
@@ -1552,7 +1552,7 @@
         <v>1936.371826171875</v>
       </c>
       <c r="C39" t="n">
-        <v>252.5473175048828</v>
+        <v>252.5473022460938</v>
       </c>
       <c r="D39" t="n">
         <v>4041.74609375</v>
@@ -1567,7 +1567,7 @@
         <v>1686.499755859375</v>
       </c>
       <c r="H39" t="n">
-        <v>767.7356567382812</v>
+        <v>767.735595703125</v>
       </c>
       <c r="I39" t="n">
         <v>1016.491577148438</v>
@@ -1578,7 +1578,7 @@
         <v>44617</v>
       </c>
       <c r="B40" t="n">
-        <v>1980.166137695312</v>
+        <v>1980.166259765625</v>
       </c>
       <c r="C40" t="n">
         <v>274.6234741210938</v>
@@ -1593,10 +1593,10 @@
         <v>78.80000305175781</v>
       </c>
       <c r="G40" t="n">
-        <v>1705.405517578125</v>
+        <v>1705.405639648438</v>
       </c>
       <c r="H40" t="n">
-        <v>779.1195068359375</v>
+        <v>779.1194458007812</v>
       </c>
       <c r="I40" t="n">
         <v>1065.739990234375</v>
@@ -1625,7 +1625,7 @@
         <v>1743.505004882812</v>
       </c>
       <c r="H41" t="n">
-        <v>762.9601440429688</v>
+        <v>762.9600830078125</v>
       </c>
       <c r="I41" t="n">
         <v>1103.585205078125</v>
@@ -1636,13 +1636,13 @@
         <v>44622</v>
       </c>
       <c r="B42" t="n">
-        <v>1988.050048828125</v>
+        <v>1988.050170898438</v>
       </c>
       <c r="C42" t="n">
         <v>282.5940856933594</v>
       </c>
       <c r="D42" t="n">
-        <v>4272.49755859375</v>
+        <v>4272.4970703125</v>
       </c>
       <c r="E42" t="n">
         <v>4295.14990234375</v>
@@ -1651,7 +1651,7 @@
         <v>79.84999847412109</v>
       </c>
       <c r="G42" t="n">
-        <v>1712.555297851562</v>
+        <v>1712.55517578125</v>
       </c>
       <c r="H42" t="n">
         <v>750.9010009765625</v>
@@ -1697,10 +1697,10 @@
         <v>1933.054931640625</v>
       </c>
       <c r="C44" t="n">
-        <v>272.1115112304688</v>
+        <v>272.1115417480469</v>
       </c>
       <c r="D44" t="n">
-        <v>4143.59765625</v>
+        <v>4143.59814453125</v>
       </c>
       <c r="E44" t="n">
         <v>4110.2001953125</v>
@@ -1723,7 +1723,7 @@
         <v>44627</v>
       </c>
       <c r="B45" t="n">
-        <v>1874.983032226562</v>
+        <v>1874.98291015625</v>
       </c>
       <c r="C45" t="n">
         <v>266.9910278320312</v>
@@ -1738,13 +1738,13 @@
         <v>79</v>
       </c>
       <c r="G45" t="n">
-        <v>1568.5546875</v>
+        <v>1568.554565429688</v>
       </c>
       <c r="H45" t="n">
         <v>666.197265625</v>
       </c>
       <c r="I45" t="n">
-        <v>1059.864013671875</v>
+        <v>1059.864135742188</v>
       </c>
     </row>
     <row r="46">
@@ -1752,7 +1752,7 @@
         <v>44628</v>
       </c>
       <c r="B46" t="n">
-        <v>1886.472290039062</v>
+        <v>1886.472412109375</v>
       </c>
       <c r="C46" t="n">
         <v>265.0104370117188</v>
@@ -1767,10 +1767,10 @@
         <v>78.15000152587891</v>
       </c>
       <c r="G46" t="n">
-        <v>1591.635131835938</v>
+        <v>1591.635009765625</v>
       </c>
       <c r="H46" t="n">
-        <v>675.941162109375</v>
+        <v>675.9412231445312</v>
       </c>
       <c r="I46" t="n">
         <v>1073.70751953125</v>
@@ -1799,7 +1799,7 @@
         <v>1622.776733398438</v>
       </c>
       <c r="H47" t="n">
-        <v>708.93505859375</v>
+        <v>708.9351196289062</v>
       </c>
       <c r="I47" t="n">
         <v>1139.139770507812</v>
@@ -1816,7 +1816,7 @@
         <v>289.5502624511719</v>
       </c>
       <c r="D48" t="n">
-        <v>4117.3486328125</v>
+        <v>4117.34912109375</v>
       </c>
       <c r="E48" t="n">
         <v>4168.60009765625</v>
@@ -1842,10 +1842,10 @@
         <v>1963.196533203125</v>
       </c>
       <c r="C49" t="n">
-        <v>284.4780578613281</v>
+        <v>284.4780883789062</v>
       </c>
       <c r="D49" t="n">
-        <v>4145.89404296875</v>
+        <v>4145.8935546875</v>
       </c>
       <c r="E49" t="n">
         <v>4198.9501953125</v>
@@ -1857,7 +1857,7 @@
         <v>1658.956909179688</v>
       </c>
       <c r="H49" t="n">
-        <v>708.8867797851562</v>
+        <v>708.8868408203125</v>
       </c>
       <c r="I49" t="n">
         <v>1164.037841796875</v>
@@ -1868,7 +1868,7 @@
         <v>44634</v>
       </c>
       <c r="B50" t="n">
-        <v>1978.723999023438</v>
+        <v>1978.72412109375</v>
       </c>
       <c r="C50" t="n">
         <v>284.2365112304688</v>
@@ -1883,7 +1883,7 @@
         <v>79.30000305175781</v>
       </c>
       <c r="G50" t="n">
-        <v>1676.3271484375</v>
+        <v>1676.327026367188</v>
       </c>
       <c r="H50" t="n">
         <v>716.9906005859375</v>
@@ -1900,10 +1900,10 @@
         <v>1980.935424804688</v>
       </c>
       <c r="C51" t="n">
-        <v>279.8406372070312</v>
+        <v>279.8406066894531</v>
       </c>
       <c r="D51" t="n">
-        <v>4275.890625</v>
+        <v>4275.89111328125</v>
       </c>
       <c r="E51" t="n">
         <v>4231.0498046875</v>
@@ -1915,7 +1915,7 @@
         <v>1673.16015625</v>
       </c>
       <c r="H51" t="n">
-        <v>734.3558349609375</v>
+        <v>734.3558959960938</v>
       </c>
       <c r="I51" t="n">
         <v>1153.531005859375</v>
@@ -1929,10 +1929,10 @@
         <v>2047.083374023438</v>
       </c>
       <c r="C52" t="n">
-        <v>307.8101806640625</v>
+        <v>307.8101501464844</v>
       </c>
       <c r="D52" t="n">
-        <v>4404.64111328125</v>
+        <v>4404.640625</v>
       </c>
       <c r="E52" t="n">
         <v>4169.5498046875</v>
@@ -1947,7 +1947,7 @@
         <v>746.3668212890625</v>
       </c>
       <c r="I52" t="n">
-        <v>1166.47802734375</v>
+        <v>1166.477905273438</v>
       </c>
     </row>
     <row r="53">
@@ -1970,7 +1970,7 @@
         <v>80.84999847412109</v>
       </c>
       <c r="G53" t="n">
-        <v>1715.818237304688</v>
+        <v>1715.818115234375</v>
       </c>
       <c r="H53" t="n">
         <v>766.3850708007812</v>
@@ -1990,7 +1990,7 @@
         <v>295.0089111328125</v>
       </c>
       <c r="D54" t="n">
-        <v>4499.65576171875</v>
+        <v>4499.65625</v>
       </c>
       <c r="E54" t="n">
         <v>4095.199951171875</v>
@@ -2031,10 +2031,10 @@
         <v>1702.526611328125</v>
       </c>
       <c r="H55" t="n">
-        <v>757.895263671875</v>
+        <v>757.8953247070312</v>
       </c>
       <c r="I55" t="n">
-        <v>1281.10888671875</v>
+        <v>1281.109008789062</v>
       </c>
     </row>
     <row r="56">
@@ -2057,13 +2057,13 @@
         <v>80.75</v>
       </c>
       <c r="G56" t="n">
-        <v>1696.000610351562</v>
+        <v>1696.00048828125</v>
       </c>
       <c r="H56" t="n">
         <v>746.8008422851562</v>
       </c>
       <c r="I56" t="n">
-        <v>1294.952270507812</v>
+        <v>1294.952392578125</v>
       </c>
     </row>
     <row r="57">
@@ -2071,13 +2071,13 @@
         <v>44644</v>
       </c>
       <c r="B57" t="n">
-        <v>2000.212524414062</v>
+        <v>2000.21240234375</v>
       </c>
       <c r="C57" t="n">
         <v>291.3375854492188</v>
       </c>
       <c r="D57" t="n">
-        <v>4314.765625</v>
+        <v>4314.76513671875</v>
       </c>
       <c r="E57" t="n">
         <v>4042.85009765625</v>
@@ -2089,7 +2089,7 @@
         <v>1700.127319335938</v>
       </c>
       <c r="H57" t="n">
-        <v>738.64892578125</v>
+        <v>738.6489868164062</v>
       </c>
       <c r="I57" t="n">
         <v>1271.647705078125</v>
@@ -2100,7 +2100,7 @@
         <v>44645</v>
       </c>
       <c r="B58" t="n">
-        <v>1984.636962890625</v>
+        <v>1984.637084960938</v>
       </c>
       <c r="C58" t="n">
         <v>298.9217224121094</v>
@@ -2115,7 +2115,7 @@
         <v>80.59999847412109</v>
       </c>
       <c r="G58" t="n">
-        <v>1680.501831054688</v>
+        <v>1680.501708984375</v>
       </c>
       <c r="H58" t="n">
         <v>737.7806396484375</v>
@@ -2158,13 +2158,13 @@
         <v>44649</v>
       </c>
       <c r="B60" t="n">
-        <v>2046.506958007812</v>
+        <v>2046.506713867188</v>
       </c>
       <c r="C60" t="n">
         <v>289.5019226074219</v>
       </c>
       <c r="D60" t="n">
-        <v>4224.640625</v>
+        <v>4224.64013671875</v>
       </c>
       <c r="E60" t="n">
         <v>4006.10009765625</v>
@@ -2179,7 +2179,7 @@
         <v>746.0773315429688</v>
       </c>
       <c r="I60" t="n">
-        <v>1271.000244140625</v>
+        <v>1271.000366210938</v>
       </c>
     </row>
     <row r="61">
@@ -2187,10 +2187,10 @@
         <v>44650</v>
       </c>
       <c r="B61" t="n">
-        <v>2067.9951171875</v>
+        <v>2067.994873046875</v>
       </c>
       <c r="C61" t="n">
-        <v>287.7628784179688</v>
+        <v>287.7629089355469</v>
       </c>
       <c r="D61" t="n">
         <v>4357.8310546875</v>
@@ -2205,7 +2205,7 @@
         <v>1702.094604492188</v>
       </c>
       <c r="H61" t="n">
-        <v>765.3720092773438</v>
+        <v>765.3720703125</v>
       </c>
       <c r="I61" t="n">
         <v>1251.978149414062</v>
@@ -2216,13 +2216,13 @@
         <v>44651</v>
       </c>
       <c r="B62" t="n">
-        <v>2068.427978515625</v>
+        <v>2068.427734375</v>
       </c>
       <c r="C62" t="n">
-        <v>285.8789367675781</v>
+        <v>285.87890625</v>
       </c>
       <c r="D62" t="n">
-        <v>4300.44287109375</v>
+        <v>4300.443359375</v>
       </c>
       <c r="E62" t="n">
         <v>4003.35009765625</v>
@@ -2277,10 +2277,10 @@
         <v>2094.2265625</v>
       </c>
       <c r="C64" t="n">
-        <v>310.5636291503906</v>
+        <v>310.5636596679688</v>
       </c>
       <c r="D64" t="n">
-        <v>4395.8076171875</v>
+        <v>4395.80810546875</v>
       </c>
       <c r="E64" t="n">
         <v>4106.64990234375</v>
@@ -2303,13 +2303,13 @@
         <v>44656</v>
       </c>
       <c r="B65" t="n">
-        <v>2124.067138671875</v>
+        <v>2124.06689453125</v>
       </c>
       <c r="C65" t="n">
         <v>299.5014038085938</v>
       </c>
       <c r="D65" t="n">
-        <v>4629.70361328125</v>
+        <v>4629.703125</v>
       </c>
       <c r="E65" t="n">
         <v>4109.7001953125</v>
@@ -2321,7 +2321,7 @@
         <v>1762.026977539062</v>
       </c>
       <c r="H65" t="n">
-        <v>807.0485229492188</v>
+        <v>807.048583984375</v>
       </c>
       <c r="I65" t="n">
         <v>1313.825073242188</v>
@@ -2335,7 +2335,7 @@
         <v>2119.966552734375</v>
       </c>
       <c r="C66" t="n">
-        <v>299.8395690917969</v>
+        <v>299.839599609375</v>
       </c>
       <c r="D66" t="n">
         <v>4583.44287109375</v>
@@ -2350,7 +2350,7 @@
         <v>1778.101684570312</v>
       </c>
       <c r="H66" t="n">
-        <v>798.6553955078125</v>
+        <v>798.6553344726562</v>
       </c>
       <c r="I66" t="n">
         <v>1322.88818359375</v>
@@ -2367,7 +2367,7 @@
         <v>314.5247802734375</v>
       </c>
       <c r="D67" t="n">
-        <v>4454.74267578125</v>
+        <v>4454.7431640625</v>
       </c>
       <c r="E67" t="n">
         <v>4159.7001953125</v>
@@ -2376,13 +2376,13 @@
         <v>82.5</v>
       </c>
       <c r="G67" t="n">
-        <v>1752.670043945312</v>
+        <v>1752.669921875</v>
       </c>
       <c r="H67" t="n">
         <v>804.8779296875</v>
       </c>
       <c r="I67" t="n">
-        <v>1302.421752929688</v>
+        <v>1302.421875</v>
       </c>
     </row>
     <row r="68">
@@ -2396,7 +2396,7 @@
         <v>317.1333618164062</v>
       </c>
       <c r="D68" t="n">
-        <v>4467.0693359375</v>
+        <v>4467.06982421875</v>
       </c>
       <c r="E68" t="n">
         <v>4146.25</v>
@@ -2405,10 +2405,10 @@
         <v>83.40000152587891</v>
       </c>
       <c r="G68" t="n">
-        <v>1756.940673828125</v>
+        <v>1756.940551757812</v>
       </c>
       <c r="H68" t="n">
-        <v>827.1632690429688</v>
+        <v>827.163330078125</v>
       </c>
       <c r="I68" t="n">
         <v>1264.47705078125</v>
@@ -2448,13 +2448,13 @@
         <v>44663</v>
       </c>
       <c r="B70" t="n">
-        <v>2155.439208984375</v>
+        <v>2155.43896484375</v>
       </c>
       <c r="C70" t="n">
         <v>300.5641784667969</v>
       </c>
       <c r="D70" t="n">
-        <v>4338.56884765625</v>
+        <v>4338.5693359375</v>
       </c>
       <c r="E70" t="n">
         <v>4088.699951171875</v>
@@ -2483,7 +2483,7 @@
         <v>304.2355041503906</v>
       </c>
       <c r="D71" t="n">
-        <v>4423.25439453125</v>
+        <v>4423.2548828125</v>
       </c>
       <c r="E71" t="n">
         <v>4090.89990234375</v>
@@ -2492,7 +2492,7 @@
         <v>83.90000152587891</v>
       </c>
       <c r="G71" t="n">
-        <v>1689.810668945312</v>
+        <v>1689.810791015625</v>
       </c>
       <c r="H71" t="n">
         <v>835.5564575195312</v>
@@ -2506,7 +2506,7 @@
         <v>44669</v>
       </c>
       <c r="B72" t="n">
-        <v>2129.551025390625</v>
+        <v>2129.55126953125</v>
       </c>
       <c r="C72" t="n">
         <v>322.3504943847656</v>
@@ -2524,10 +2524,10 @@
         <v>1668.265747070312</v>
       </c>
       <c r="H72" t="n">
-        <v>843.2742919921875</v>
+        <v>843.2743530273438</v>
       </c>
       <c r="I72" t="n">
-        <v>1218.514892578125</v>
+        <v>1218.515014648438</v>
       </c>
     </row>
     <row r="73">
@@ -2535,7 +2535,7 @@
         <v>44670</v>
       </c>
       <c r="B73" t="n">
-        <v>2032.025756835938</v>
+        <v>2032.025634765625</v>
       </c>
       <c r="C73" t="n">
         <v>345.2478637695312</v>
@@ -2553,7 +2553,7 @@
         <v>1636.980224609375</v>
       </c>
       <c r="H73" t="n">
-        <v>841.7307739257812</v>
+        <v>841.7308349609375</v>
       </c>
       <c r="I73" t="n">
         <v>1243.363403320312</v>
@@ -2570,7 +2570,7 @@
         <v>339.2095031738281</v>
       </c>
       <c r="D74" t="n">
-        <v>4212.9130859375</v>
+        <v>4212.91357421875</v>
       </c>
       <c r="E74" t="n">
         <v>4054.800048828125</v>
@@ -2596,7 +2596,7 @@
         <v>2243.083740234375</v>
       </c>
       <c r="C75" t="n">
-        <v>327.3743896484375</v>
+        <v>327.3743591308594</v>
       </c>
       <c r="D75" t="n">
         <v>4286.32080078125</v>
@@ -2614,7 +2614,7 @@
         <v>878.873046875</v>
       </c>
       <c r="I75" t="n">
-        <v>1280.561401367188</v>
+        <v>1280.561279296875</v>
       </c>
     </row>
     <row r="76">
@@ -2628,7 +2628,7 @@
         <v>336.069580078125</v>
       </c>
       <c r="D76" t="n">
-        <v>4290.26318359375</v>
+        <v>4290.2626953125</v>
       </c>
       <c r="E76" t="n">
         <v>4028.85009765625</v>
@@ -2654,10 +2654,10 @@
         <v>2235.129638671875</v>
       </c>
       <c r="C77" t="n">
-        <v>327.3743896484375</v>
+        <v>327.3743591308594</v>
       </c>
       <c r="D77" t="n">
-        <v>4304.5849609375</v>
+        <v>4304.58544921875</v>
       </c>
       <c r="E77" t="n">
         <v>3989.199951171875</v>
@@ -2669,10 +2669,10 @@
         <v>1590.531372070312</v>
       </c>
       <c r="H77" t="n">
-        <v>872.1199340820312</v>
+        <v>872.119873046875</v>
       </c>
       <c r="I77" t="n">
-        <v>1232.408081054688</v>
+        <v>1232.408203125</v>
       </c>
     </row>
     <row r="78">
@@ -2686,7 +2686,7 @@
         <v>318.5342407226562</v>
       </c>
       <c r="D78" t="n">
-        <v>4331.83154296875</v>
+        <v>4331.83203125</v>
       </c>
       <c r="E78" t="n">
         <v>4044.25</v>
@@ -2701,7 +2701,7 @@
         <v>906.9951171875</v>
       </c>
       <c r="I78" t="n">
-        <v>1274.635375976562</v>
+        <v>1274.635498046875</v>
       </c>
     </row>
     <row r="79">
@@ -2712,7 +2712,7 @@
         <v>2321.933837890625</v>
       </c>
       <c r="C79" t="n">
-        <v>316.7952270507812</v>
+        <v>316.7951965332031</v>
       </c>
       <c r="D79" t="n">
         <v>4306.5810546875</v>
@@ -2724,13 +2724,13 @@
         <v>75.84999847412109</v>
       </c>
       <c r="G79" t="n">
-        <v>1609.437133789062</v>
+        <v>1609.437255859375</v>
       </c>
       <c r="H79" t="n">
         <v>894.1640625</v>
       </c>
       <c r="I79" t="n">
-        <v>1220.008911132812</v>
+        <v>1220.009033203125</v>
       </c>
     </row>
     <row r="80">
@@ -2738,10 +2738,10 @@
         <v>44679</v>
       </c>
       <c r="B80" t="n">
-        <v>2348.46435546875</v>
+        <v>2348.464599609375</v>
       </c>
       <c r="C80" t="n">
-        <v>318.8724060058594</v>
+        <v>318.8723754882812</v>
       </c>
       <c r="D80" t="n">
         <v>4362.77197265625</v>
@@ -2753,10 +2753,10 @@
         <v>73.84999847412109</v>
       </c>
       <c r="G80" t="n">
-        <v>1649.935791015625</v>
+        <v>1649.935913085938</v>
       </c>
       <c r="H80" t="n">
-        <v>890.3534545898438</v>
+        <v>890.3533935546875</v>
       </c>
       <c r="I80" t="n">
         <v>1220.755859375</v>
@@ -2785,7 +2785,7 @@
         <v>1626.039672851562</v>
       </c>
       <c r="H81" t="n">
-        <v>889.5816040039062</v>
+        <v>889.58154296875</v>
       </c>
       <c r="I81" t="n">
         <v>1223.395141601562</v>
@@ -2796,7 +2796,7 @@
         <v>44683</v>
       </c>
       <c r="B82" t="n">
-        <v>2319.265869140625</v>
+        <v>2319.26611328125</v>
       </c>
       <c r="C82" t="n">
         <v>307.2787780761719</v>
@@ -2814,7 +2814,7 @@
         <v>1611.740478515625</v>
       </c>
       <c r="H82" t="n">
-        <v>888.8579711914062</v>
+        <v>888.8580322265625</v>
       </c>
       <c r="I82" t="n">
         <v>1215.228515625</v>
@@ -2825,7 +2825,7 @@
         <v>44685</v>
       </c>
       <c r="B83" t="n">
-        <v>2272.7265625</v>
+        <v>2272.726806640625</v>
       </c>
       <c r="C83" t="n">
         <v>286.989990234375</v>
@@ -2846,7 +2846,7 @@
         <v>864.4984741210938</v>
       </c>
       <c r="I83" t="n">
-        <v>1208.306762695312</v>
+        <v>1208.306884765625</v>
       </c>
     </row>
     <row r="84">
@@ -2875,7 +2875,7 @@
         <v>867.3444213867188</v>
       </c>
       <c r="I84" t="n">
-        <v>1207.410400390625</v>
+        <v>1207.410522460938</v>
       </c>
     </row>
     <row r="85">
@@ -2898,10 +2898,10 @@
         <v>60.5</v>
       </c>
       <c r="G85" t="n">
-        <v>1557.038330078125</v>
+        <v>1557.038452148438</v>
       </c>
       <c r="H85" t="n">
-        <v>862.327880859375</v>
+        <v>862.3278198242188</v>
       </c>
       <c r="I85" t="n">
         <v>1142.077758789062</v>
@@ -2915,7 +2915,7 @@
         <v>2206.326171875</v>
       </c>
       <c r="C86" t="n">
-        <v>291.7240600585938</v>
+        <v>291.7240905761719</v>
       </c>
       <c r="D86" t="n">
         <v>3816.83251953125</v>
@@ -2930,7 +2930,7 @@
         <v>1550.992553710938</v>
       </c>
       <c r="H86" t="n">
-        <v>863.7266845703125</v>
+        <v>863.7267456054688</v>
       </c>
       <c r="I86" t="n">
         <v>1099.3525390625</v>
@@ -2944,7 +2944,7 @@
         <v>2172.38525390625</v>
       </c>
       <c r="C87" t="n">
-        <v>289.0671997070312</v>
+        <v>289.0671691894531</v>
       </c>
       <c r="D87" t="n">
         <v>3672.96240234375</v>
@@ -2956,10 +2956,10 @@
         <v>52.45000076293945</v>
       </c>
       <c r="G87" t="n">
-        <v>1543.123168945312</v>
+        <v>1543.123046875</v>
       </c>
       <c r="H87" t="n">
-        <v>857.021728515625</v>
+        <v>857.0217895507812</v>
       </c>
       <c r="I87" t="n">
         <v>1055.830688476562</v>
@@ -2970,13 +2970,13 @@
         <v>44692</v>
       </c>
       <c r="B88" t="n">
-        <v>2141.852783203125</v>
+        <v>2141.85302734375</v>
       </c>
       <c r="C88" t="n">
         <v>282.5940856933594</v>
       </c>
       <c r="D88" t="n">
-        <v>3504.98876953125</v>
+        <v>3504.988525390625</v>
       </c>
       <c r="E88" t="n">
         <v>3339.699951171875</v>
@@ -3020,7 +3020,7 @@
         <v>834.7365112304688</v>
       </c>
       <c r="I89" t="n">
-        <v>1006.731384277344</v>
+        <v>1006.7314453125</v>
       </c>
     </row>
     <row r="90">
@@ -3031,7 +3031,7 @@
         <v>2088.14990234375</v>
       </c>
       <c r="C90" t="n">
-        <v>248.8276824951172</v>
+        <v>248.8276977539062</v>
       </c>
       <c r="D90" t="n">
         <v>3364.86083984375</v>
@@ -3043,13 +3043,13 @@
         <v>56.84999847412109</v>
       </c>
       <c r="G90" t="n">
-        <v>1472.634399414062</v>
+        <v>1472.63427734375</v>
       </c>
       <c r="H90" t="n">
-        <v>858.1312866210938</v>
+        <v>858.1312255859375</v>
       </c>
       <c r="I90" t="n">
-        <v>1027.795288085938</v>
+        <v>1027.795166015625</v>
       </c>
     </row>
     <row r="91">
@@ -3063,7 +3063,7 @@
         <v>230.7127075195312</v>
       </c>
       <c r="D91" t="n">
-        <v>3336.416259765625</v>
+        <v>3336.41650390625</v>
       </c>
       <c r="E91" t="n">
         <v>3561.10009765625</v>
@@ -3075,7 +3075,7 @@
         <v>1480.695678710938</v>
       </c>
       <c r="H91" t="n">
-        <v>871.4927368164062</v>
+        <v>871.4927978515625</v>
       </c>
       <c r="I91" t="n">
         <v>1034.916137695312</v>
@@ -3086,13 +3086,13 @@
         <v>44698</v>
       </c>
       <c r="B92" t="n">
-        <v>2199.360595703125</v>
+        <v>2199.3603515625</v>
       </c>
       <c r="C92" t="n">
-        <v>246.0742340087891</v>
+        <v>246.07421875</v>
       </c>
       <c r="D92" t="n">
-        <v>3482.3330078125</v>
+        <v>3482.333251953125</v>
       </c>
       <c r="E92" t="n">
         <v>3657</v>
@@ -3118,10 +3118,10 @@
         <v>2210.03173828125</v>
       </c>
       <c r="C93" t="n">
-        <v>232.9831085205078</v>
+        <v>232.9831237792969</v>
       </c>
       <c r="D93" t="n">
-        <v>3497.603271484375</v>
+        <v>3497.60302734375</v>
       </c>
       <c r="E93" t="n">
         <v>3664.050048828125</v>
@@ -3133,7 +3133,7 @@
         <v>1509.102172851562</v>
       </c>
       <c r="H93" t="n">
-        <v>881.0919189453125</v>
+        <v>881.0919799804688</v>
       </c>
       <c r="I93" t="n">
         <v>1080.629150390625</v>
@@ -3162,10 +3162,10 @@
         <v>1485.5419921875</v>
       </c>
       <c r="H94" t="n">
-        <v>851.4263305664062</v>
+        <v>851.4263916015625</v>
       </c>
       <c r="I94" t="n">
-        <v>1032.42626953125</v>
+        <v>1032.426391601562</v>
       </c>
     </row>
     <row r="95">
@@ -3173,7 +3173,7 @@
         <v>44701</v>
       </c>
       <c r="B95" t="n">
-        <v>2212.7490234375</v>
+        <v>2212.748779296875</v>
       </c>
       <c r="C95" t="n">
         <v>224.5777587890625</v>
@@ -3188,7 +3188,7 @@
         <v>58.04999923706055</v>
       </c>
       <c r="G95" t="n">
-        <v>1545.186401367188</v>
+        <v>1545.186279296875</v>
       </c>
       <c r="H95" t="n">
         <v>871.9269409179688</v>
@@ -3202,13 +3202,13 @@
         <v>44704</v>
       </c>
       <c r="B96" t="n">
-        <v>2187.05859375</v>
+        <v>2187.058349609375</v>
       </c>
       <c r="C96" t="n">
         <v>217.8631439208984</v>
       </c>
       <c r="D96" t="n">
-        <v>3502.09423828125</v>
+        <v>3502.094482421875</v>
       </c>
       <c r="E96" t="n">
         <v>3574.10009765625</v>
@@ -3220,7 +3220,7 @@
         <v>1577.863647460938</v>
       </c>
       <c r="H96" t="n">
-        <v>908.6834106445312</v>
+        <v>908.683349609375</v>
       </c>
       <c r="I96" t="n">
         <v>1062.086547851562</v>
@@ -3246,10 +3246,10 @@
         <v>64.94999694824219</v>
       </c>
       <c r="G97" t="n">
-        <v>1560.7333984375</v>
+        <v>1560.733276367188</v>
       </c>
       <c r="H97" t="n">
-        <v>913.458740234375</v>
+        <v>913.4586791992188</v>
       </c>
       <c r="I97" t="n">
         <v>1072.654541015625</v>
@@ -3289,13 +3289,13 @@
         <v>44707</v>
       </c>
       <c r="B99" t="n">
-        <v>2181.722900390625</v>
+        <v>2181.72265625</v>
       </c>
       <c r="C99" t="n">
         <v>209.457763671875</v>
       </c>
       <c r="D99" t="n">
-        <v>3358.1240234375</v>
+        <v>3358.124267578125</v>
       </c>
       <c r="E99" t="n">
         <v>3577.449951171875</v>
@@ -3304,7 +3304,7 @@
         <v>60.45000076293945</v>
       </c>
       <c r="G99" t="n">
-        <v>1501.472900390625</v>
+        <v>1501.472778320312</v>
       </c>
       <c r="H99" t="n">
         <v>897.010009765625</v>
@@ -3318,13 +3318,13 @@
         <v>44708</v>
       </c>
       <c r="B100" t="n">
-        <v>2171.891357421875</v>
+        <v>2171.89111328125</v>
       </c>
       <c r="C100" t="n">
-        <v>211.8247985839844</v>
+        <v>211.8247833251953</v>
       </c>
       <c r="D100" t="n">
-        <v>3414.5146484375</v>
+        <v>3414.514404296875</v>
       </c>
       <c r="E100" t="n">
         <v>3613.85009765625</v>
@@ -3336,7 +3336,7 @@
         <v>1535.781494140625</v>
       </c>
       <c r="H100" t="n">
-        <v>919.2471313476562</v>
+        <v>919.2470703125</v>
       </c>
       <c r="I100" t="n">
         <v>1065.22705078125</v>
@@ -3347,7 +3347,7 @@
         <v>44711</v>
       </c>
       <c r="B101" t="n">
-        <v>2182.068603515625</v>
+        <v>2182.06884765625</v>
       </c>
       <c r="C101" t="n">
         <v>222.4039459228516</v>
@@ -3362,10 +3362,10 @@
         <v>71.05000305175781</v>
       </c>
       <c r="G101" t="n">
-        <v>1593.89013671875</v>
+        <v>1593.890258789062</v>
       </c>
       <c r="H101" t="n">
-        <v>963.142578125</v>
+        <v>963.1425170898438</v>
       </c>
       <c r="I101" t="n">
         <v>1115.52490234375</v>
@@ -3405,10 +3405,10 @@
         <v>44713</v>
       </c>
       <c r="B103" t="n">
-        <v>2169.71728515625</v>
+        <v>2169.717529296875</v>
       </c>
       <c r="C103" t="n">
-        <v>225.2540435791016</v>
+        <v>225.2540283203125</v>
       </c>
       <c r="D103" t="n">
         <v>3884.7509765625</v>
@@ -3463,7 +3463,7 @@
         <v>44715</v>
       </c>
       <c r="B105" t="n">
-        <v>2107.714111328125</v>
+        <v>2107.71435546875</v>
       </c>
       <c r="C105" t="n">
         <v>222.3073577880859</v>
@@ -3498,7 +3498,7 @@
         <v>226.1718902587891</v>
       </c>
       <c r="D106" t="n">
-        <v>3662.083740234375</v>
+        <v>3662.08349609375</v>
       </c>
       <c r="E106" t="n">
         <v>3734.75</v>
@@ -3507,10 +3507,10 @@
         <v>69.90000152587891</v>
       </c>
       <c r="G106" t="n">
-        <v>1574.072875976562</v>
+        <v>1574.07275390625</v>
       </c>
       <c r="H106" t="n">
-        <v>999.41650390625</v>
+        <v>999.4165649414062</v>
       </c>
       <c r="I106" t="n">
         <v>1101.41748046875</v>
@@ -3521,13 +3521,13 @@
         <v>44719</v>
       </c>
       <c r="B107" t="n">
-        <v>2112.901611328125</v>
+        <v>2112.90185546875</v>
       </c>
       <c r="C107" t="n">
-        <v>225.6888275146484</v>
+        <v>225.6888122558594</v>
       </c>
       <c r="D107" t="n">
-        <v>3610.58349609375</v>
+        <v>3610.583740234375</v>
       </c>
       <c r="E107" t="n">
         <v>3726.699951171875</v>
@@ -3539,7 +3539,7 @@
         <v>1525.368896484375</v>
       </c>
       <c r="H107" t="n">
-        <v>1005.783996582031</v>
+        <v>1005.783874511719</v>
       </c>
       <c r="I107" t="n">
         <v>1081.57763671875</v>
@@ -3550,13 +3550,13 @@
         <v>44720</v>
       </c>
       <c r="B108" t="n">
-        <v>2110.085693359375</v>
+        <v>2110.08544921875</v>
       </c>
       <c r="C108" t="n">
         <v>221.8725738525391</v>
       </c>
       <c r="D108" t="n">
-        <v>3585.9814453125</v>
+        <v>3585.981689453125</v>
       </c>
       <c r="E108" t="n">
         <v>3739.39990234375</v>
@@ -3594,10 +3594,10 @@
         <v>68.69999694824219</v>
       </c>
       <c r="G109" t="n">
-        <v>1530.791137695312</v>
+        <v>1530.791015625</v>
       </c>
       <c r="H109" t="n">
-        <v>1008.243835449219</v>
+        <v>1008.243896484375</v>
       </c>
       <c r="I109" t="n">
         <v>1080.979370117188</v>
@@ -3626,7 +3626,7 @@
         <v>1521.194213867188</v>
       </c>
       <c r="H110" t="n">
-        <v>999.947265625</v>
+        <v>999.9472045898438</v>
       </c>
       <c r="I110" t="n">
         <v>1109.94189453125</v>
@@ -3652,10 +3652,10 @@
         <v>67.5</v>
       </c>
       <c r="G111" t="n">
-        <v>1470.283081054688</v>
+        <v>1470.283203125</v>
       </c>
       <c r="H111" t="n">
-        <v>968.8828125</v>
+        <v>968.8827514648438</v>
       </c>
       <c r="I111" t="n">
         <v>1083.372192382812</v>
@@ -3669,7 +3669,7 @@
         <v>2090.91650390625</v>
       </c>
       <c r="C112" t="n">
-        <v>197.0429382324219</v>
+        <v>197.0429534912109</v>
       </c>
       <c r="D112" t="n">
         <v>3406.38037109375</v>
@@ -3681,10 +3681,10 @@
         <v>70</v>
       </c>
       <c r="G112" t="n">
-        <v>1482.375122070312</v>
+        <v>1482.375</v>
       </c>
       <c r="H112" t="n">
-        <v>983.3054809570312</v>
+        <v>983.3055419921875</v>
       </c>
       <c r="I112" t="n">
         <v>1066.223999023438</v>
@@ -3727,10 +3727,10 @@
         <v>2059.445556640625</v>
       </c>
       <c r="C114" t="n">
-        <v>195.5937652587891</v>
+        <v>195.59375</v>
       </c>
       <c r="D114" t="n">
-        <v>3344.1513671875</v>
+        <v>3344.151123046875</v>
       </c>
       <c r="E114" t="n">
         <v>3682.60009765625</v>
@@ -3742,7 +3742,7 @@
         <v>1465.820678710938</v>
       </c>
       <c r="H114" t="n">
-        <v>969.7992553710938</v>
+        <v>969.7991943359375</v>
       </c>
       <c r="I114" t="n">
         <v>1074.798095703125</v>
@@ -3817,7 +3817,7 @@
         <v>194.4827117919922</v>
       </c>
       <c r="D117" t="n">
-        <v>3455.33544921875</v>
+        <v>3455.335205078125</v>
       </c>
       <c r="E117" t="n">
         <v>3519.550048828125</v>
@@ -3840,13 +3840,13 @@
         <v>44734</v>
       </c>
       <c r="B118" t="n">
-        <v>2037.756713867188</v>
+        <v>2037.756591796875</v>
       </c>
       <c r="C118" t="n">
-        <v>184.91796875</v>
+        <v>184.9179534912109</v>
       </c>
       <c r="D118" t="n">
-        <v>3359.17236328125</v>
+        <v>3359.172119140625</v>
       </c>
       <c r="E118" t="n">
         <v>3486.35009765625</v>
@@ -3855,10 +3855,10 @@
         <v>67.59999847412109</v>
       </c>
       <c r="G118" t="n">
-        <v>1419.131958007812</v>
+        <v>1419.132080078125</v>
       </c>
       <c r="H118" t="n">
-        <v>949.1056518554688</v>
+        <v>949.105712890625</v>
       </c>
       <c r="I118" t="n">
         <v>1017.720825195312</v>
@@ -3869,10 +3869,10 @@
         <v>44735</v>
       </c>
       <c r="B119" t="n">
-        <v>2065.52197265625</v>
+        <v>2065.522216796875</v>
       </c>
       <c r="C119" t="n">
-        <v>186.8019409179688</v>
+        <v>186.8019561767578</v>
       </c>
       <c r="D119" t="n">
         <v>3385.421142578125</v>
@@ -3898,7 +3898,7 @@
         <v>44736</v>
       </c>
       <c r="B120" t="n">
-        <v>2073.2294921875</v>
+        <v>2073.229248046875</v>
       </c>
       <c r="C120" t="n">
         <v>188.4443664550781</v>
@@ -3930,10 +3930,10 @@
         <v>2090.66943359375</v>
       </c>
       <c r="C121" t="n">
-        <v>200.2794952392578</v>
+        <v>200.2795104980469</v>
       </c>
       <c r="D121" t="n">
-        <v>3629.097412109375</v>
+        <v>3629.09765625</v>
       </c>
       <c r="E121" t="n">
         <v>3408.60009765625</v>
@@ -3945,7 +3945,7 @@
         <v>1473.881958007812</v>
       </c>
       <c r="H121" t="n">
-        <v>1044.517944335938</v>
+        <v>1044.517822265625</v>
       </c>
       <c r="I121" t="n">
         <v>1045.935424804688</v>
@@ -3985,13 +3985,13 @@
         <v>44741</v>
       </c>
       <c r="B123" t="n">
-        <v>2129.600341796875</v>
+        <v>2129.6005859375</v>
       </c>
       <c r="C123" t="n">
-        <v>199.2167510986328</v>
+        <v>199.2167358398438</v>
       </c>
       <c r="D123" t="n">
-        <v>3643.819091796875</v>
+        <v>3643.81884765625</v>
       </c>
       <c r="E123" t="n">
         <v>3445.25</v>
@@ -4003,7 +4003,7 @@
         <v>1485.494140625</v>
       </c>
       <c r="H123" t="n">
-        <v>1072.54345703125</v>
+        <v>1072.543334960938</v>
       </c>
       <c r="I123" t="n">
         <v>1105.903930664062</v>
@@ -4017,7 +4017,7 @@
         <v>2096.69677734375</v>
       </c>
       <c r="C124" t="n">
-        <v>196.4149627685547</v>
+        <v>196.4149475097656</v>
       </c>
       <c r="D124" t="n">
         <v>3568.066162109375</v>
@@ -4032,7 +4032,7 @@
         <v>1495.426879882812</v>
       </c>
       <c r="H124" t="n">
-        <v>1054.599365234375</v>
+        <v>1054.599487304688</v>
       </c>
       <c r="I124" t="n">
         <v>1070.909912109375</v>
@@ -4043,13 +4043,13 @@
         <v>44743</v>
       </c>
       <c r="B125" t="n">
-        <v>2141.309326171875</v>
+        <v>2141.3095703125</v>
       </c>
       <c r="C125" t="n">
         <v>196.5115661621094</v>
       </c>
       <c r="D125" t="n">
-        <v>3588.72607421875</v>
+        <v>3588.726318359375</v>
       </c>
       <c r="E125" t="n">
         <v>3388.75</v>
@@ -4058,7 +4058,7 @@
         <v>56.15000152587891</v>
       </c>
       <c r="G125" t="n">
-        <v>1508.766357421875</v>
+        <v>1508.766479492188</v>
       </c>
       <c r="H125" t="n">
         <v>1068.298583984375</v>
@@ -4072,10 +4072,10 @@
         <v>44746</v>
       </c>
       <c r="B126" t="n">
-        <v>2138.839111328125</v>
+        <v>2138.83935546875</v>
       </c>
       <c r="C126" t="n">
-        <v>196.656494140625</v>
+        <v>196.6565093994141</v>
       </c>
       <c r="D126" t="n">
         <v>3584.434326171875</v>
@@ -4090,7 +4090,7 @@
         <v>1517.931274414062</v>
       </c>
       <c r="H126" t="n">
-        <v>1052.718017578125</v>
+        <v>1052.718139648438</v>
       </c>
       <c r="I126" t="n">
         <v>1114.827026367188</v>
@@ -4101,13 +4101,13 @@
         <v>44747</v>
       </c>
       <c r="B127" t="n">
-        <v>2122.486083984375</v>
+        <v>2122.486328125</v>
       </c>
       <c r="C127" t="n">
-        <v>194.2411499023438</v>
+        <v>194.2411651611328</v>
       </c>
       <c r="D127" t="n">
-        <v>3517.813720703125</v>
+        <v>3517.81396484375</v>
       </c>
       <c r="E127" t="n">
         <v>3639.050048828125</v>
@@ -4136,7 +4136,7 @@
         <v>196.5598754882812</v>
       </c>
       <c r="D128" t="n">
-        <v>3661.634521484375</v>
+        <v>3661.63427734375</v>
       </c>
       <c r="E128" t="n">
         <v>3792</v>
@@ -4145,10 +4145,10 @@
         <v>54.34999847412109</v>
       </c>
       <c r="G128" t="n">
-        <v>1493.411499023438</v>
+        <v>1493.411376953125</v>
       </c>
       <c r="H128" t="n">
-        <v>1065.597534179688</v>
+        <v>1065.597412109375</v>
       </c>
       <c r="I128" t="n">
         <v>1168.46484375</v>
@@ -4159,7 +4159,7 @@
         <v>44749</v>
       </c>
       <c r="B129" t="n">
-        <v>2142.544921875</v>
+        <v>2142.544677734375</v>
       </c>
       <c r="C129" t="n">
         <v>200.2311859130859</v>
@@ -4191,7 +4191,7 @@
         <v>2143.53271484375</v>
       </c>
       <c r="C130" t="n">
-        <v>198.2506103515625</v>
+        <v>198.2506256103516</v>
       </c>
       <c r="D130" t="n">
         <v>3650.80517578125</v>
@@ -4203,10 +4203,10 @@
         <v>54.79999923706055</v>
       </c>
       <c r="G130" t="n">
-        <v>1619.417846679688</v>
+        <v>1619.41796875</v>
       </c>
       <c r="H130" t="n">
-        <v>1093.622924804688</v>
+        <v>1093.622802734375</v>
       </c>
       <c r="I130" t="n">
         <v>1200.617431640625</v>
@@ -4261,7 +4261,7 @@
         <v>59</v>
       </c>
       <c r="G132" t="n">
-        <v>1587.07666015625</v>
+        <v>1587.076538085938</v>
       </c>
       <c r="H132" t="n">
         <v>1106.212768554688</v>
@@ -4304,13 +4304,13 @@
         <v>44756</v>
       </c>
       <c r="B134" t="n">
-        <v>2134.59033203125</v>
+        <v>2134.590576171875</v>
       </c>
       <c r="C134" t="n">
-        <v>195.5937652587891</v>
+        <v>195.59375</v>
       </c>
       <c r="D134" t="n">
-        <v>3692.12548828125</v>
+        <v>3692.125244140625</v>
       </c>
       <c r="E134" t="n">
         <v>3924.85009765625</v>
@@ -4319,7 +4319,7 @@
         <v>55.65000152587891</v>
       </c>
       <c r="G134" t="n">
-        <v>1579.783081054688</v>
+        <v>1579.782958984375</v>
       </c>
       <c r="H134" t="n">
         <v>1113.633178710938</v>
@@ -4362,13 +4362,13 @@
         <v>44760</v>
       </c>
       <c r="B136" t="n">
-        <v>2148.12744140625</v>
+        <v>2148.127685546875</v>
       </c>
       <c r="C136" t="n">
-        <v>202.6465148925781</v>
+        <v>202.6465301513672</v>
       </c>
       <c r="D136" t="n">
-        <v>3804.15771484375</v>
+        <v>3804.157470703125</v>
       </c>
       <c r="E136" t="n">
         <v>3945.75</v>
@@ -4391,7 +4391,7 @@
         <v>44761</v>
       </c>
       <c r="B137" t="n">
-        <v>2142.9892578125</v>
+        <v>2142.989501953125</v>
       </c>
       <c r="C137" t="n">
         <v>206.5593566894531</v>
@@ -4420,7 +4420,7 @@
         <v>44762</v>
       </c>
       <c r="B138" t="n">
-        <v>2133.206787109375</v>
+        <v>2133.20703125</v>
       </c>
       <c r="C138" t="n">
         <v>206.1246032714844</v>
@@ -4449,7 +4449,7 @@
         <v>44763</v>
       </c>
       <c r="B139" t="n">
-        <v>2148.6708984375</v>
+        <v>2148.670654296875</v>
       </c>
       <c r="C139" t="n">
         <v>227.3795471191406</v>
@@ -4481,10 +4481,10 @@
         <v>2165.863525390625</v>
       </c>
       <c r="C140" t="n">
-        <v>239.3113098144531</v>
+        <v>239.3112945556641</v>
       </c>
       <c r="D140" t="n">
-        <v>3849.169921875</v>
+        <v>3849.169677734375</v>
       </c>
       <c r="E140" t="n">
         <v>3963.39990234375</v>
@@ -4507,7 +4507,7 @@
         <v>44767</v>
       </c>
       <c r="B141" t="n">
-        <v>2178.21484375</v>
+        <v>2178.215087890625</v>
       </c>
       <c r="C141" t="n">
         <v>239.8909759521484</v>
@@ -4542,7 +4542,7 @@
         <v>232.210205078125</v>
       </c>
       <c r="D142" t="n">
-        <v>3678.80078125</v>
+        <v>3678.801025390625</v>
       </c>
       <c r="E142" t="n">
         <v>3932.39990234375</v>
@@ -4565,13 +4565,13 @@
         <v>44769</v>
       </c>
       <c r="B143" t="n">
-        <v>2164.18408203125</v>
+        <v>2164.183837890625</v>
       </c>
       <c r="C143" t="n">
         <v>236.0747528076172</v>
       </c>
       <c r="D143" t="n">
-        <v>3693.073486328125</v>
+        <v>3693.0732421875</v>
       </c>
       <c r="E143" t="n">
         <v>4000.949951171875</v>
@@ -4594,13 +4594,13 @@
         <v>44770</v>
       </c>
       <c r="B144" t="n">
-        <v>2154.796875</v>
+        <v>2154.797119140625</v>
       </c>
       <c r="C144" t="n">
         <v>247.4751129150391</v>
       </c>
       <c r="D144" t="n">
-        <v>3571.5595703125</v>
+        <v>3571.559326171875</v>
       </c>
       <c r="E144" t="n">
         <v>4147.7998046875</v>
@@ -4623,7 +4623,7 @@
         <v>44771</v>
       </c>
       <c r="B145" t="n">
-        <v>2200.8916015625</v>
+        <v>2200.891845703125</v>
       </c>
       <c r="C145" t="n">
         <v>274.0437927246094</v>
@@ -4652,13 +4652,13 @@
         <v>44774</v>
       </c>
       <c r="B146" t="n">
-        <v>2200.052001953125</v>
+        <v>2200.05224609375</v>
       </c>
       <c r="C146" t="n">
-        <v>266.5563049316406</v>
+        <v>266.5562744140625</v>
       </c>
       <c r="D146" t="n">
-        <v>3740.93017578125</v>
+        <v>3740.930419921875</v>
       </c>
       <c r="E146" t="n">
         <v>4307.64990234375</v>
@@ -4681,7 +4681,7 @@
         <v>44775</v>
       </c>
       <c r="B147" t="n">
-        <v>2201.138671875</v>
+        <v>2201.138916015625</v>
       </c>
       <c r="C147" t="n">
         <v>256.6533813476562</v>
@@ -4713,7 +4713,7 @@
         <v>2209.78466796875</v>
       </c>
       <c r="C148" t="n">
-        <v>270.3724975585938</v>
+        <v>270.3724670410156</v>
       </c>
       <c r="D148" t="n">
         <v>3748.0166015625</v>
@@ -4768,7 +4768,7 @@
         <v>44778</v>
       </c>
       <c r="B150" t="n">
-        <v>2227.965576171875</v>
+        <v>2227.9658203125</v>
       </c>
       <c r="C150" t="n">
         <v>263.8993835449219</v>
@@ -4826,13 +4826,13 @@
         <v>44783</v>
       </c>
       <c r="B152" t="n">
-        <v>2200.496826171875</v>
+        <v>2200.49658203125</v>
       </c>
       <c r="C152" t="n">
         <v>266.8944091796875</v>
       </c>
       <c r="D152" t="n">
-        <v>3838.490478515625</v>
+        <v>3838.49072265625</v>
       </c>
       <c r="E152" t="n">
         <v>4250.7001953125</v>
@@ -4913,10 +4913,10 @@
         <v>44789</v>
       </c>
       <c r="B155" t="n">
-        <v>2244.318603515625</v>
+        <v>2244.31884765625</v>
       </c>
       <c r="C155" t="n">
-        <v>289.7434387207031</v>
+        <v>289.7434692382812</v>
       </c>
       <c r="D155" t="n">
         <v>3894.111572265625</v>
@@ -4945,7 +4945,7 @@
         <v>2255.978271484375</v>
       </c>
       <c r="C156" t="n">
-        <v>283.3186645507812</v>
+        <v>283.3186950683594</v>
       </c>
       <c r="D156" t="n">
         <v>4000.46044921875</v>
@@ -4974,7 +4974,7 @@
         <v>2295.2060546875</v>
       </c>
       <c r="C157" t="n">
-        <v>279.0193481445312</v>
+        <v>279.0193786621094</v>
       </c>
       <c r="D157" t="n">
         <v>4062.372314453125</v>
@@ -5000,7 +5000,7 @@
         <v>44792</v>
       </c>
       <c r="B158" t="n">
-        <v>2322.87255859375</v>
+        <v>2322.872802734375</v>
       </c>
       <c r="C158" t="n">
         <v>276.7006530761719</v>
@@ -5145,7 +5145,7 @@
         <v>44799</v>
       </c>
       <c r="B163" t="n">
-        <v>2258.30029296875</v>
+        <v>2258.300537109375</v>
       </c>
       <c r="C163" t="n">
         <v>279.7923278808594</v>
@@ -5177,7 +5177,7 @@
         <v>2261.363525390625</v>
       </c>
       <c r="C164" t="n">
-        <v>272.8844299316406</v>
+        <v>272.8844604492188</v>
       </c>
       <c r="D164" t="n">
         <v>3975.845458984375</v>
@@ -5203,10 +5203,10 @@
         <v>44803</v>
       </c>
       <c r="B165" t="n">
-        <v>2272.33154296875</v>
+        <v>2272.331298828125</v>
       </c>
       <c r="C165" t="n">
-        <v>303.6074829101562</v>
+        <v>303.6074523925781</v>
       </c>
       <c r="D165" t="n">
         <v>4097.8720703125</v>
@@ -5261,7 +5261,7 @@
         <v>44806</v>
       </c>
       <c r="B167" t="n">
-        <v>2262.79638671875</v>
+        <v>2262.796142578125</v>
       </c>
       <c r="C167" t="n">
         <v>330.0795288085938</v>
@@ -5348,7 +5348,7 @@
         <v>44811</v>
       </c>
       <c r="B170" t="n">
-        <v>2376.724365234375</v>
+        <v>2376.72412109375</v>
       </c>
       <c r="C170" t="n">
         <v>323.8962707519531</v>
@@ -5377,7 +5377,7 @@
         <v>44812</v>
       </c>
       <c r="B171" t="n">
-        <v>2392.3359375</v>
+        <v>2392.335693359375</v>
       </c>
       <c r="C171" t="n">
         <v>348.7742614746094</v>
@@ -5438,7 +5438,7 @@
         <v>2471.087646484375</v>
       </c>
       <c r="C173" t="n">
-        <v>348.484375</v>
+        <v>348.4844055175781</v>
       </c>
       <c r="D173" t="n">
         <v>4491.16259765625</v>
@@ -5464,7 +5464,7 @@
         <v>44817</v>
       </c>
       <c r="B174" t="n">
-        <v>2542.18115234375</v>
+        <v>2542.181396484375</v>
       </c>
       <c r="C174" t="n">
         <v>351.5215148925781</v>
@@ -5551,7 +5551,7 @@
         <v>44820</v>
       </c>
       <c r="B177" t="n">
-        <v>2580.420654296875</v>
+        <v>2580.4208984375</v>
       </c>
       <c r="C177" t="n">
         <v>331.4863586425781</v>
@@ -5696,7 +5696,7 @@
         <v>44827</v>
       </c>
       <c r="B182" t="n">
-        <v>2459.27978515625</v>
+        <v>2459.279541015625</v>
       </c>
       <c r="C182" t="n">
         <v>379.1984558105469</v>
@@ -5812,7 +5812,7 @@
         <v>44833</v>
       </c>
       <c r="B186" t="n">
-        <v>2345.79638671875</v>
+        <v>2345.796630859375</v>
       </c>
       <c r="C186" t="n">
         <v>308.85498046875</v>
@@ -5928,7 +5928,7 @@
         <v>44840</v>
       </c>
       <c r="B190" t="n">
-        <v>2353.40478515625</v>
+        <v>2353.405029296875</v>
       </c>
       <c r="C190" t="n">
         <v>327.3225708007812</v>
@@ -5986,7 +5986,7 @@
         <v>44844</v>
       </c>
       <c r="B192" t="n">
-        <v>2341.0537109375</v>
+        <v>2341.053955078125</v>
       </c>
       <c r="C192" t="n">
         <v>334.0336303710938</v>
@@ -6102,7 +6102,7 @@
         <v>44848</v>
       </c>
       <c r="B196" t="n">
-        <v>2216.948486328125</v>
+        <v>2216.9482421875</v>
       </c>
       <c r="C196" t="n">
         <v>317.7213439941406</v>
@@ -6160,7 +6160,7 @@
         <v>44852</v>
       </c>
       <c r="B198" t="n">
-        <v>2192.838623046875</v>
+        <v>2192.8388671875</v>
       </c>
       <c r="C198" t="n">
         <v>323.9915161132812</v>
@@ -6189,7 +6189,7 @@
         <v>44853</v>
       </c>
       <c r="B199" t="n">
-        <v>2219.71533203125</v>
+        <v>2219.715087890625</v>
       </c>
       <c r="C199" t="n">
         <v>320.5625610351562</v>
@@ -6218,7 +6218,7 @@
         <v>44854</v>
       </c>
       <c r="B200" t="n">
-        <v>2260.375732421875</v>
+        <v>2260.37548828125</v>
       </c>
       <c r="C200" t="n">
         <v>317.7703552246094</v>
@@ -6334,7 +6334,7 @@
         <v>44861</v>
       </c>
       <c r="B204" t="n">
-        <v>2285.47314453125</v>
+        <v>2285.472900390625</v>
       </c>
       <c r="C204" t="n">
         <v>316.986572265625</v>
@@ -6479,7 +6479,7 @@
         <v>44868</v>
       </c>
       <c r="B209" t="n">
-        <v>2426.12890625</v>
+        <v>2426.129150390625</v>
       </c>
       <c r="C209" t="n">
         <v>311.1083068847656</v>
@@ -6537,7 +6537,7 @@
         <v>44872</v>
       </c>
       <c r="B211" t="n">
-        <v>2455.37646484375</v>
+        <v>2455.376708984375</v>
       </c>
       <c r="C211" t="n">
         <v>306.8465576171875</v>
@@ -6711,7 +6711,7 @@
         <v>44881</v>
       </c>
       <c r="B217" t="n">
-        <v>2436.25732421875</v>
+        <v>2436.257080078125</v>
       </c>
       <c r="C217" t="n">
         <v>306.8465576171875</v>
@@ -6943,7 +6943,7 @@
         <v>44893</v>
       </c>
       <c r="B225" t="n">
-        <v>2497.025390625</v>
+        <v>2497.025146484375</v>
       </c>
       <c r="C225" t="n">
         <v>289.9954528808594</v>
@@ -7146,7 +7146,7 @@
         <v>44902</v>
       </c>
       <c r="B232" t="n">
-        <v>2574.9365234375</v>
+        <v>2574.936767578125</v>
       </c>
       <c r="C232" t="n">
         <v>307.4343566894531</v>
@@ -7175,7 +7175,7 @@
         <v>44903</v>
       </c>
       <c r="B233" t="n">
-        <v>2590.054443359375</v>
+        <v>2590.0546875</v>
       </c>
       <c r="C233" t="n">
         <v>304.2992858886719</v>
@@ -7204,7 +7204,7 @@
         <v>44904</v>
       </c>
       <c r="B234" t="n">
-        <v>2588.325439453125</v>
+        <v>2588.32568359375</v>
       </c>
       <c r="C234" t="n">
         <v>303.2215881347656</v>
@@ -7233,7 +7233,7 @@
         <v>44907</v>
       </c>
       <c r="B235" t="n">
-        <v>2610.952880859375</v>
+        <v>2610.95263671875</v>
       </c>
       <c r="C235" t="n">
         <v>309.1488342285156</v>
@@ -7320,7 +7320,7 @@
         <v>44910</v>
       </c>
       <c r="B238" t="n">
-        <v>2604.13525390625</v>
+        <v>2604.135009765625</v>
       </c>
       <c r="C238" t="n">
         <v>311.059326171875</v>
@@ -7378,7 +7378,7 @@
         <v>44914</v>
       </c>
       <c r="B240" t="n">
-        <v>2607.09912109375</v>
+        <v>2607.099365234375</v>
       </c>
       <c r="C240" t="n">
         <v>313.4596252441406</v>
@@ -7436,7 +7436,7 @@
         <v>44916</v>
       </c>
       <c r="B242" t="n">
-        <v>2510.71044921875</v>
+        <v>2510.710205078125</v>
       </c>
       <c r="C242" t="n">
         <v>302.7807312011719</v>
@@ -7465,7 +7465,7 @@
         <v>44917</v>
       </c>
       <c r="B243" t="n">
-        <v>2483.78466796875</v>
+        <v>2483.784423828125</v>
       </c>
       <c r="C243" t="n">
         <v>291.2201232910156</v>
@@ -7494,7 +7494,7 @@
         <v>44918</v>
       </c>
       <c r="B244" t="n">
-        <v>2345.845947265625</v>
+        <v>2345.84619140625</v>
       </c>
       <c r="C244" t="n">
         <v>279.41455078125</v>
@@ -7581,7 +7581,7 @@
         <v>44923</v>
       </c>
       <c r="B247" t="n">
-        <v>2426.12890625</v>
+        <v>2426.129150390625</v>
       </c>
       <c r="C247" t="n">
         <v>312.0880126953125</v>
@@ -7668,7 +7668,7 @@
         <v>44928</v>
       </c>
       <c r="B250" t="n">
-        <v>2410.71435546875</v>
+        <v>2410.714599609375</v>
       </c>
       <c r="C250" t="n">
         <v>317.8193359375</v>
@@ -7726,7 +7726,7 @@
         <v>44930</v>
       </c>
       <c r="B252" t="n">
-        <v>2380.627197265625</v>
+        <v>2380.626953125</v>
       </c>
       <c r="C252" t="n">
         <v>319.7297973632812</v>
@@ -7813,7 +7813,7 @@
         <v>44935</v>
       </c>
       <c r="B255" t="n">
-        <v>2435.318115234375</v>
+        <v>2435.318359375</v>
       </c>
       <c r="C255" t="n">
         <v>319.5338439941406</v>
@@ -7842,7 +7842,7 @@
         <v>44936</v>
       </c>
       <c r="B256" t="n">
-        <v>2390.162353515625</v>
+        <v>2390.162109375</v>
       </c>
       <c r="C256" t="n">
         <v>313.3616333007812</v>
@@ -7900,7 +7900,7 @@
         <v>44938</v>
       </c>
       <c r="B258" t="n">
-        <v>2336.26123046875</v>
+        <v>2336.261474609375</v>
       </c>
       <c r="C258" t="n">
         <v>318.1622619628906</v>
@@ -7958,7 +7958,7 @@
         <v>44942</v>
       </c>
       <c r="B260" t="n">
-        <v>2333.297119140625</v>
+        <v>2333.296875</v>
       </c>
       <c r="C260" t="n">
         <v>314.6842651367188</v>
@@ -8190,7 +8190,7 @@
         <v>44953</v>
       </c>
       <c r="B268" t="n">
-        <v>1857.379150390625</v>
+        <v>1857.379272460938</v>
       </c>
       <c r="C268" t="n">
         <v>299.4987182617188</v>
@@ -8219,7 +8219,7 @@
         <v>44956</v>
       </c>
       <c r="B269" t="n">
-        <v>1881.488891601562</v>
+        <v>1881.48876953125</v>
       </c>
       <c r="C269" t="n">
         <v>324.0894775390625</v>
@@ -8306,7 +8306,7 @@
         <v>44959</v>
       </c>
       <c r="B272" t="n">
-        <v>1819.33740234375</v>
+        <v>1819.337280273438</v>
       </c>
       <c r="C272" t="n">
         <v>309.6877136230469</v>
@@ -8393,7 +8393,7 @@
         <v>44964</v>
       </c>
       <c r="B275" t="n">
-        <v>1970.318969726562</v>
+        <v>1970.319091796875</v>
       </c>
       <c r="C275" t="n">
         <v>329.428955078125</v>
@@ -8422,7 +8422,7 @@
         <v>44965</v>
       </c>
       <c r="B276" t="n">
-        <v>1950.260498046875</v>
+        <v>1950.260620117188</v>
       </c>
       <c r="C276" t="n">
         <v>330.1147766113281</v>
@@ -8451,7 +8451,7 @@
         <v>44966</v>
       </c>
       <c r="B277" t="n">
-        <v>1893.197631835938</v>
+        <v>1893.19775390625</v>
       </c>
       <c r="C277" t="n">
         <v>339.6669616699219</v>
@@ -8480,7 +8480,7 @@
         <v>44967</v>
       </c>
       <c r="B278" t="n">
-        <v>1858.021484375</v>
+        <v>1858.021606445312</v>
       </c>
       <c r="C278" t="n">
         <v>332.8089599609375</v>
@@ -8509,7 +8509,7 @@
         <v>44970</v>
       </c>
       <c r="B279" t="n">
-        <v>1801.452758789062</v>
+        <v>1801.452880859375</v>
       </c>
       <c r="C279" t="n">
         <v>322.2770690917969</v>
@@ -8654,7 +8654,7 @@
         <v>44977</v>
       </c>
       <c r="B284" t="n">
-        <v>1828.625610351562</v>
+        <v>1828.62548828125</v>
       </c>
       <c r="C284" t="n">
         <v>355.1954345703125</v>
@@ -8828,7 +8828,7 @@
         <v>44985</v>
       </c>
       <c r="B290" t="n">
-        <v>1711.090942382812</v>
+        <v>1711.091064453125</v>
       </c>
       <c r="C290" t="n">
         <v>338.9321899414062</v>
@@ -8944,7 +8944,7 @@
         <v>44991</v>
       </c>
       <c r="B294" t="n">
-        <v>1843.595336914062</v>
+        <v>1843.59521484375</v>
       </c>
       <c r="C294" t="n">
         <v>351.2275695800781</v>
@@ -8973,7 +8973,7 @@
         <v>44993</v>
       </c>
       <c r="B295" t="n">
-        <v>1864.048828125</v>
+        <v>1864.048950195312</v>
       </c>
       <c r="C295" t="n">
         <v>362.59228515625</v>
@@ -9002,7 +9002,7 @@
         <v>44994</v>
       </c>
       <c r="B296" t="n">
-        <v>1837.963012695312</v>
+        <v>1837.963134765625</v>
       </c>
       <c r="C296" t="n">
         <v>352.4522399902344</v>
@@ -9060,7 +9060,7 @@
         <v>44998</v>
       </c>
       <c r="B298" t="n">
-        <v>1748.935424804688</v>
+        <v>1748.935302734375</v>
       </c>
       <c r="C298" t="n">
         <v>342.2632141113281</v>
@@ -9176,7 +9176,7 @@
         <v>45002</v>
       </c>
       <c r="B302" t="n">
-        <v>1709.806518554688</v>
+        <v>1709.806640625</v>
       </c>
       <c r="C302" t="n">
         <v>367.4418640136719</v>
@@ -9321,7 +9321,7 @@
         <v>45009</v>
       </c>
       <c r="B307" t="n">
-        <v>1680.608154296875</v>
+        <v>1680.608276367188</v>
       </c>
       <c r="C307" t="n">
         <v>333.5437622070312</v>
@@ -9379,7 +9379,7 @@
         <v>45013</v>
       </c>
       <c r="B309" t="n">
-        <v>1594.742309570312</v>
+        <v>1594.742431640625</v>
       </c>
       <c r="C309" t="n">
         <v>310.3244934082031</v>
@@ -9495,7 +9495,7 @@
         <v>45021</v>
       </c>
       <c r="B313" t="n">
-        <v>1667.861694335938</v>
+        <v>1667.86181640625</v>
       </c>
       <c r="C313" t="n">
         <v>345.59423828125</v>
@@ -9524,7 +9524,7 @@
         <v>45022</v>
       </c>
       <c r="B314" t="n">
-        <v>1691.62548828125</v>
+        <v>1691.625610351562</v>
       </c>
       <c r="C314" t="n">
         <v>355.538330078125</v>
@@ -9582,7 +9582,7 @@
         <v>45027</v>
       </c>
       <c r="B316" t="n">
-        <v>1716.723388671875</v>
+        <v>1716.723266601562</v>
       </c>
       <c r="C316" t="n">
         <v>352.8441162109375</v>
@@ -9640,7 +9640,7 @@
         <v>45029</v>
       </c>
       <c r="B318" t="n">
-        <v>1746.514526367188</v>
+        <v>1746.514404296875</v>
       </c>
       <c r="C318" t="n">
         <v>368.4705810546875</v>
@@ -9727,7 +9727,7 @@
         <v>45035</v>
       </c>
       <c r="B321" t="n">
-        <v>1728.481811523438</v>
+        <v>1728.481689453125</v>
       </c>
       <c r="C321" t="n">
         <v>382.6764221191406</v>
@@ -9756,7 +9756,7 @@
         <v>45036</v>
       </c>
       <c r="B322" t="n">
-        <v>1717.4150390625</v>
+        <v>1717.414916992188</v>
       </c>
       <c r="C322" t="n">
         <v>388.015869140625</v>
@@ -9785,7 +9785,7 @@
         <v>45037</v>
       </c>
       <c r="B323" t="n">
-        <v>1697.504638671875</v>
+        <v>1697.504760742188</v>
       </c>
       <c r="C323" t="n">
         <v>379.1494750976562</v>
@@ -9814,7 +9814,7 @@
         <v>45040</v>
       </c>
       <c r="B324" t="n">
-        <v>1714.005981445312</v>
+        <v>1714.006103515625</v>
       </c>
       <c r="C324" t="n">
         <v>383.4112548828125</v>
@@ -9843,7 +9843,7 @@
         <v>45041</v>
       </c>
       <c r="B325" t="n">
-        <v>1715.48828125</v>
+        <v>1715.488159179688</v>
       </c>
       <c r="C325" t="n">
         <v>388.7506713867188</v>
@@ -10017,7 +10017,7 @@
         <v>45050</v>
       </c>
       <c r="B331" t="n">
-        <v>1745.279418945312</v>
+        <v>1745.279296875</v>
       </c>
       <c r="C331" t="n">
         <v>405.0628967285156</v>
@@ -10075,7 +10075,7 @@
         <v>45054</v>
       </c>
       <c r="B333" t="n">
-        <v>1745.625122070312</v>
+        <v>1745.625244140625</v>
       </c>
       <c r="C333" t="n">
         <v>523.8043212890625</v>
@@ -10104,7 +10104,7 @@
         <v>45055</v>
       </c>
       <c r="B334" t="n">
-        <v>1738.362670898438</v>
+        <v>1738.36279296875</v>
       </c>
       <c r="C334" t="n">
         <v>540.9492797851562</v>
@@ -10394,7 +10394,7 @@
         <v>45069</v>
       </c>
       <c r="B344" t="n">
-        <v>1797.796752929688</v>
+        <v>1797.796875</v>
       </c>
       <c r="C344" t="n">
         <v>585.5263061523438</v>
@@ -10452,7 +10452,7 @@
         <v>45071</v>
       </c>
       <c r="B346" t="n">
-        <v>1756.988403320312</v>
+        <v>1756.98828125</v>
       </c>
       <c r="C346" t="n">
         <v>570.4876098632812</v>
@@ -10510,7 +10510,7 @@
         <v>45075</v>
       </c>
       <c r="B348" t="n">
-        <v>1773.044921875</v>
+        <v>1773.045043945312</v>
       </c>
       <c r="C348" t="n">
         <v>555.595947265625</v>
@@ -10684,7 +10684,7 @@
         <v>45083</v>
       </c>
       <c r="B354" t="n">
-        <v>1834.208374023438</v>
+        <v>1834.208251953125</v>
       </c>
       <c r="C354" t="n">
         <v>578.3253784179688</v>
@@ -10713,7 +10713,7 @@
         <v>45084</v>
       </c>
       <c r="B355" t="n">
-        <v>1829.71240234375</v>
+        <v>1829.712280273438</v>
       </c>
       <c r="C355" t="n">
         <v>582.4402465820312</v>
@@ -10771,7 +10771,7 @@
         <v>45086</v>
       </c>
       <c r="B357" t="n">
-        <v>1815.434326171875</v>
+        <v>1815.434448242188</v>
       </c>
       <c r="C357" t="n">
         <v>562.3560180664062</v>
@@ -10800,7 +10800,7 @@
         <v>45089</v>
       </c>
       <c r="B358" t="n">
-        <v>1816.66943359375</v>
+        <v>1816.669555664062</v>
       </c>
       <c r="C358" t="n">
         <v>562.8948974609375</v>
@@ -10916,7 +10916,7 @@
         <v>45093</v>
       </c>
       <c r="B362" t="n">
-        <v>1833.368408203125</v>
+        <v>1833.368286132812</v>
       </c>
       <c r="C362" t="n">
         <v>590.0819702148438</v>
@@ -10974,7 +10974,7 @@
         <v>45097</v>
       </c>
       <c r="B364" t="n">
-        <v>1816.323608398438</v>
+        <v>1816.323486328125</v>
       </c>
       <c r="C364" t="n">
         <v>580.774658203125</v>
@@ -11032,7 +11032,7 @@
         <v>45099</v>
       </c>
       <c r="B366" t="n">
-        <v>1809.950317382812</v>
+        <v>1809.950439453125</v>
       </c>
       <c r="C366" t="n">
         <v>569.8509521484375</v>
@@ -11119,7 +11119,7 @@
         <v>45104</v>
       </c>
       <c r="B369" t="n">
-        <v>1767.313842773438</v>
+        <v>1767.31396484375</v>
       </c>
       <c r="C369" t="n">
         <v>564.5603637695312</v>
@@ -11148,7 +11148,7 @@
         <v>45105</v>
       </c>
       <c r="B370" t="n">
-        <v>1790.781372070312</v>
+        <v>1790.78125</v>
       </c>
       <c r="C370" t="n">
         <v>563.8256225585938</v>
@@ -11177,7 +11177,7 @@
         <v>45107</v>
       </c>
       <c r="B371" t="n">
-        <v>1792.115234375</v>
+        <v>1792.115112304688</v>
       </c>
       <c r="C371" t="n">
         <v>565.589111328125</v>
@@ -11206,7 +11206,7 @@
         <v>45110</v>
       </c>
       <c r="B372" t="n">
-        <v>1803.379516601562</v>
+        <v>1803.379638671875</v>
       </c>
       <c r="C372" t="n">
         <v>565.3931274414062</v>
@@ -11264,7 +11264,7 @@
         <v>45112</v>
       </c>
       <c r="B374" t="n">
-        <v>1799.130737304688</v>
+        <v>1799.130859375</v>
       </c>
       <c r="C374" t="n">
         <v>557.0166015625</v>
@@ -11293,7 +11293,7 @@
         <v>45113</v>
       </c>
       <c r="B375" t="n">
-        <v>1798.686157226562</v>
+        <v>1798.68603515625</v>
       </c>
       <c r="C375" t="n">
         <v>558.7800903320312</v>
@@ -32814,7 +32814,7 @@
         <v>45138</v>
       </c>
       <c r="B36" t="n">
-        <v>11.82699444070869</v>
+        <v>11.82700205782887</v>
       </c>
       <c r="C36" t="n">
         <v>6.902824894362691</v>
@@ -32843,7 +32843,7 @@
         <v>45107</v>
       </c>
       <c r="B37" t="n">
-        <v>2.053795897246391</v>
+        <v>2.053788945830259</v>
       </c>
       <c r="C37" t="n">
         <v>0.9265767892046028</v>
@@ -32930,7 +32930,7 @@
         <v>45016</v>
       </c>
       <c r="B40" t="n">
-        <v>-3.724651691839564</v>
+        <v>-3.724658560183458</v>
       </c>
       <c r="C40" t="n">
         <v>-6.402662313515151</v>
@@ -32959,7 +32959,7 @@
         <v>44985</v>
       </c>
       <c r="B41" t="n">
-        <v>-12.02053498593027</v>
+        <v>-12.02052870941945</v>
       </c>
       <c r="C41" t="n">
         <v>5.940900817164319</v>
@@ -33104,10 +33104,10 @@
         <v>44834</v>
       </c>
       <c r="B46" t="n">
-        <v>5.041950175504195</v>
+        <v>5.041961461273736</v>
       </c>
       <c r="C46" t="n">
-        <v>7.778835435302023</v>
+        <v>7.778846268860296</v>
       </c>
       <c r="D46" t="n">
         <v>6.528254827379198</v>
@@ -33133,10 +33133,10 @@
         <v>44804</v>
       </c>
       <c r="B47" t="n">
-        <v>3.245954564756026</v>
+        <v>3.245932019080078</v>
       </c>
       <c r="C47" t="n">
-        <v>10.78794374126031</v>
+        <v>10.78793260523792</v>
       </c>
       <c r="D47" t="n">
         <v>10.97152689612049</v>
@@ -33162,10 +33162,10 @@
         <v>44773</v>
       </c>
       <c r="B48" t="n">
-        <v>4.969475097431664</v>
+        <v>4.969486741491402</v>
       </c>
       <c r="C48" t="n">
-        <v>39.52286977623416</v>
+        <v>39.52288061527705</v>
       </c>
       <c r="D48" t="n">
         <v>3.493705250410906</v>
@@ -33180,7 +33180,7 @@
         <v>17.51668518694323</v>
       </c>
       <c r="H48" t="n">
-        <v>7.612383812628787</v>
+        <v>7.612371356452319</v>
       </c>
       <c r="I48" t="n">
         <v>18.10268082573436</v>
@@ -33194,7 +33194,7 @@
         <v>-3.477534039682906</v>
       </c>
       <c r="C49" t="n">
-        <v>-11.12567848891192</v>
+        <v>-11.12568539324601</v>
       </c>
       <c r="D49" t="n">
         <v>-7.352214765781406</v>
@@ -33209,7 +33209,7 @@
         <v>-5.817458248402985</v>
       </c>
       <c r="H49" t="n">
-        <v>5.68472943946754</v>
+        <v>5.684741672518645</v>
       </c>
       <c r="I49" t="n">
         <v>-4.439296543597415</v>
@@ -33238,7 +33238,7 @@
         <v>-2.351935739431132</v>
       </c>
       <c r="H50" t="n">
-        <v>12.17329375388725</v>
+        <v>12.17330145021882</v>
       </c>
       <c r="I50" t="n">
         <v>-8.397600771019675</v>
@@ -33249,13 +33249,13 @@
         <v>44681</v>
       </c>
       <c r="B51" t="n">
-        <v>11.2527901281839</v>
+        <v>11.25280325957121</v>
       </c>
       <c r="C51" t="n">
-        <v>7.891173920205019</v>
+        <v>7.891185437589665</v>
       </c>
       <c r="D51" t="n">
-        <v>2.029564769344372</v>
+        <v>2.029553184696153</v>
       </c>
       <c r="E51" t="n">
         <v>-1.476266032562323</v>
@@ -33267,7 +33267,7 @@
         <v>-4.146751384601122</v>
       </c>
       <c r="H51" t="n">
-        <v>14.32644849612872</v>
+        <v>14.32644065206741</v>
       </c>
       <c r="I51" t="n">
         <v>-3.6926680353216</v>
@@ -33278,13 +33278,13 @@
         <v>44651</v>
       </c>
       <c r="B52" t="n">
-        <v>2.977303021266264</v>
+        <v>2.977290866652527</v>
       </c>
       <c r="C52" t="n">
-        <v>4.373903496310572</v>
+        <v>4.373892354395781</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2188379406257601</v>
+        <v>-0.2188266112645776</v>
       </c>
       <c r="E52" t="n">
         <v>-7.764350626507688</v>
@@ -33296,7 +33296,7 @@
         <v>-2.70262966073932</v>
       </c>
       <c r="H52" t="n">
-        <v>1.985218160883484</v>
+        <v>1.985226319480327</v>
       </c>
       <c r="I52" t="n">
         <v>15.1069456903713</v>
@@ -33313,7 +33313,7 @@
         <v>-7.999358310367644</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.019405581946554</v>
+        <v>-2.019416458355139</v>
       </c>
       <c r="E53" t="n">
         <v>5.492969597525055</v>
@@ -33325,7 +33325,7 @@
         <v>-4.842337998278301</v>
       </c>
       <c r="H53" t="n">
-        <v>-10.71913429906422</v>
+        <v>-10.71913506465438</v>
       </c>
       <c r="I53" t="n">
         <v>7.483149452435223</v>
@@ -33733,7 +33733,7 @@
         <v>45199</v>
       </c>
       <c r="B13" t="n">
-        <v>11.51388242551192</v>
+        <v>11.51389002130441</v>
       </c>
       <c r="C13" t="n">
         <v>56.2260942834339</v>
@@ -33762,7 +33762,7 @@
         <v>45107</v>
       </c>
       <c r="B14" t="n">
-        <v>8.787185453039736</v>
+        <v>8.787178042977327</v>
       </c>
       <c r="C14" t="n">
         <v>78.28907280990303</v>
@@ -33852,7 +33852,7 @@
         <v>13.84103762545019</v>
       </c>
       <c r="C17" t="n">
-        <v>66.59861589088032</v>
+        <v>66.59862883334304</v>
       </c>
       <c r="D17" t="n">
         <v>22.34615063813057</v>
@@ -33867,7 +33867,7 @@
         <v>20.0937885416778</v>
       </c>
       <c r="H17" t="n">
-        <v>17.20041883129586</v>
+        <v>17.20040526530049</v>
       </c>
       <c r="I17" t="n">
         <v>32.19755077400912</v>
@@ -33878,13 +33878,13 @@
         <v>44742</v>
       </c>
       <c r="B18" t="n">
-        <v>1.366680354440564</v>
+        <v>1.366692318950746</v>
       </c>
       <c r="C18" t="n">
-        <v>-31.29435662892449</v>
+        <v>-31.29435463209674</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.03026248545668</v>
+        <v>-17.03027190601259</v>
       </c>
       <c r="E18" t="n">
         <v>-14.91875517831074</v>
@@ -33896,7 +33896,7 @@
         <v>-11.84623173911773</v>
       </c>
       <c r="H18" t="n">
-        <v>35.534052717426</v>
+        <v>35.53406840554864</v>
       </c>
       <c r="I18" t="n">
         <v>-15.69651300497659</v>
@@ -33988,7 +33988,7 @@
         <v>10.28490226754897</v>
       </c>
       <c r="C2" t="n">
-        <v>49.06682023874436</v>
+        <v>49.06680961938839</v>
       </c>
       <c r="D2" t="n">
         <v>-30.77094595271642</v>
@@ -34003,10 +34003,10 @@
         <v>9.903035148493533</v>
       </c>
       <c r="H2" t="n">
-        <v>53.99405550110126</v>
+        <v>53.99406724204066</v>
       </c>
       <c r="I2" t="n">
-        <v>18.54737986411594</v>
+        <v>18.54735229206599</v>
       </c>
     </row>
     <row r="3">
@@ -34014,7 +34014,7 @@
         <v>44935</v>
       </c>
       <c r="B3" t="n">
-        <v>13.87622400470525</v>
+        <v>13.87623542079597</v>
       </c>
       <c r="C3" t="n">
         <v>51.02037519541052</v>
@@ -34032,10 +34032,10 @@
         <v>10.90658191799239</v>
       </c>
       <c r="H3" t="n">
-        <v>59.13417258411939</v>
+        <v>59.1341604811842</v>
       </c>
       <c r="I3" t="n">
-        <v>15.70185264871915</v>
+        <v>15.70186608663495</v>
       </c>
     </row>
     <row r="4">
@@ -34043,10 +34043,10 @@
         <v>44936</v>
       </c>
       <c r="B4" t="n">
-        <v>10.9170052865718</v>
+        <v>10.9169813907301</v>
       </c>
       <c r="C4" t="n">
-        <v>48.61216221281766</v>
+        <v>48.6121729671384</v>
       </c>
       <c r="D4" t="n">
         <v>-29.73600204570629</v>
@@ -34061,10 +34061,10 @@
         <v>9.495415637767145</v>
       </c>
       <c r="H4" t="n">
-        <v>58.23159167797031</v>
+        <v>58.23157975334365</v>
       </c>
       <c r="I4" t="n">
-        <v>14.45675974280536</v>
+        <v>14.45673352612735</v>
       </c>
     </row>
     <row r="5">
@@ -34072,10 +34072,10 @@
         <v>44937</v>
       </c>
       <c r="B5" t="n">
-        <v>10.50675936813605</v>
+        <v>10.50677196669487</v>
       </c>
       <c r="C5" t="n">
-        <v>52.43428270237924</v>
+        <v>52.43427165375305</v>
       </c>
       <c r="D5" t="n">
         <v>-30.55674817263825</v>
@@ -34093,7 +34093,7 @@
         <v>57.88898159556526</v>
       </c>
       <c r="I5" t="n">
-        <v>12.24962708847481</v>
+        <v>12.24961434595584</v>
       </c>
     </row>
     <row r="6">
@@ -34101,10 +34101,10 @@
         <v>44938</v>
       </c>
       <c r="B6" t="n">
-        <v>6.360872625162339</v>
+        <v>6.360871918165945</v>
       </c>
       <c r="C6" t="n">
-        <v>48.60784481841313</v>
+        <v>48.60783422697716</v>
       </c>
       <c r="D6" t="n">
         <v>-31.01197895748117</v>
@@ -34116,13 +34116,13 @@
         <v>-58.41392649903288</v>
       </c>
       <c r="G6" t="n">
-        <v>14.83058939606849</v>
+        <v>14.8305970638102</v>
       </c>
       <c r="H6" t="n">
         <v>60.84505737350923</v>
       </c>
       <c r="I6" t="n">
-        <v>11.63720025504582</v>
+        <v>11.63721287140742</v>
       </c>
     </row>
     <row r="7">
@@ -34133,7 +34133,7 @@
         <v>4.85521835037297</v>
       </c>
       <c r="C7" t="n">
-        <v>43.87224379370367</v>
+        <v>43.8722538103212</v>
       </c>
       <c r="D7" t="n">
         <v>-31.41210509226725</v>
@@ -34145,13 +34145,13 @@
         <v>-59.10138152985653</v>
       </c>
       <c r="G7" t="n">
-        <v>11.66743450783725</v>
+        <v>11.66742723533105</v>
       </c>
       <c r="H7" t="n">
-        <v>59.36099060747957</v>
+        <v>59.36097863268639</v>
       </c>
       <c r="I7" t="n">
-        <v>12.62875281404567</v>
+        <v>12.6287399288981</v>
       </c>
     </row>
     <row r="8">
@@ -34159,7 +34159,7 @@
         <v>44942</v>
       </c>
       <c r="B8" t="n">
-        <v>5.624900602117688</v>
+        <v>5.624889550233636</v>
       </c>
       <c r="C8" t="n">
         <v>37.37454828857574</v>
@@ -34180,7 +34180,7 @@
         <v>57.95831734256969</v>
       </c>
       <c r="I8" t="n">
-        <v>7.167672409116888</v>
+        <v>7.167684152965936</v>
       </c>
     </row>
     <row r="9">
@@ -34188,7 +34188,7 @@
         <v>44943</v>
       </c>
       <c r="B9" t="n">
-        <v>4.156333606736395</v>
+        <v>4.156345032440889</v>
       </c>
       <c r="C9" t="n">
         <v>36.59165377754545</v>
@@ -34220,7 +34220,7 @@
         <v>5.029381437699421</v>
       </c>
       <c r="C10" t="n">
-        <v>40.63640489222549</v>
+        <v>40.63641439249957</v>
       </c>
       <c r="D10" t="n">
         <v>-33.22681487336763</v>
@@ -34232,13 +34232,13 @@
         <v>-61.68294691110994</v>
       </c>
       <c r="G10" t="n">
-        <v>13.72990773760028</v>
+        <v>13.72991490479962</v>
       </c>
       <c r="H10" t="n">
         <v>49.07124262587799</v>
       </c>
       <c r="I10" t="n">
-        <v>3.542897476589757</v>
+        <v>3.542876006338047</v>
       </c>
     </row>
     <row r="11">
@@ -34261,13 +34261,13 @@
         <v>-61.75149989549558</v>
       </c>
       <c r="G11" t="n">
-        <v>12.59124421331503</v>
+        <v>12.59123720931044</v>
       </c>
       <c r="H11" t="n">
-        <v>51.27688107870871</v>
+        <v>51.27689193972329</v>
       </c>
       <c r="I11" t="n">
-        <v>3.040598269226424</v>
+        <v>3.040609117816007</v>
       </c>
     </row>
     <row r="12">
@@ -34275,7 +34275,7 @@
         <v>44946</v>
       </c>
       <c r="B12" t="n">
-        <v>1.775249439119597</v>
+        <v>1.775260303936577</v>
       </c>
       <c r="C12" t="n">
         <v>19.55973571149989</v>
@@ -34296,7 +34296,7 @@
         <v>47.44701448887756</v>
       </c>
       <c r="I12" t="n">
-        <v>2.24409585134826</v>
+        <v>2.244085025279929</v>
       </c>
     </row>
     <row r="13">
@@ -34319,10 +34319,10 @@
         <v>-61.66854653873215</v>
       </c>
       <c r="G13" t="n">
-        <v>11.86342872152846</v>
+        <v>11.86342168520098</v>
       </c>
       <c r="H13" t="n">
-        <v>50.42793289512968</v>
+        <v>50.42794356263573</v>
       </c>
       <c r="I13" t="n">
         <v>3.048485494135256</v>
@@ -34333,7 +34333,7 @@
         <v>44950</v>
       </c>
       <c r="B14" t="n">
-        <v>7.555571939480066</v>
+        <v>7.55558417685902</v>
       </c>
       <c r="C14" t="n">
         <v>-2.613216582295796</v>
@@ -34348,10 +34348,10 @@
         <v>-59.6749228291449</v>
       </c>
       <c r="G14" t="n">
-        <v>10.63235833563489</v>
+        <v>10.63235137226666</v>
       </c>
       <c r="H14" t="n">
-        <v>49.53558282286703</v>
+        <v>49.53559340041605</v>
       </c>
       <c r="I14" t="n">
         <v>3.184080385879118</v>
@@ -34391,10 +34391,10 @@
         <v>44953</v>
       </c>
       <c r="B16" t="n">
-        <v>-12.81324150703166</v>
+        <v>-12.81323577696042</v>
       </c>
       <c r="C16" t="n">
-        <v>-2.547243461939408</v>
+        <v>-2.547253138996641</v>
       </c>
       <c r="D16" t="n">
         <v>-45.30870648315744</v>
@@ -34409,7 +34409,7 @@
         <v>11.8329824842508</v>
       </c>
       <c r="H16" t="n">
-        <v>52.38896324491211</v>
+        <v>52.38897426077418</v>
       </c>
       <c r="I16" t="n">
         <v>-0.3061012713922229</v>
@@ -34420,13 +34420,13 @@
         <v>44956</v>
       </c>
       <c r="B17" t="n">
-        <v>-9.713393761225664</v>
+        <v>-9.713399618987728</v>
       </c>
       <c r="C17" t="n">
-        <v>4.877266675732539</v>
+        <v>4.877256318402567</v>
       </c>
       <c r="D17" t="n">
-        <v>-41.97239821174853</v>
+        <v>-41.97240435578928</v>
       </c>
       <c r="E17" t="n">
         <v>-12.11805799031</v>
@@ -34441,7 +34441,7 @@
         <v>57.39149577417957</v>
       </c>
       <c r="I17" t="n">
-        <v>5.378060376720772</v>
+        <v>5.37803733889155</v>
       </c>
     </row>
     <row r="18">
@@ -34455,7 +34455,7 @@
         <v>5.509077292783471</v>
       </c>
       <c r="D18" t="n">
-        <v>-41.06136962727867</v>
+        <v>-41.06137596161906</v>
       </c>
       <c r="E18" t="n">
         <v>-14.4831437184094</v>
@@ -34467,7 +34467,7 @@
         <v>11.75425721568923</v>
       </c>
       <c r="H18" t="n">
-        <v>63.00262260737608</v>
+        <v>63.00263467591858</v>
       </c>
       <c r="I18" t="n">
         <v>11.04513432535987</v>
@@ -34499,7 +34499,7 @@
         <v>59.18470000811795</v>
       </c>
       <c r="I19" t="n">
-        <v>19.0671555833086</v>
+        <v>19.06714844586883</v>
       </c>
     </row>
     <row r="20">
@@ -34507,13 +34507,13 @@
         <v>44959</v>
       </c>
       <c r="B20" t="n">
-        <v>-14.60666097301804</v>
+        <v>-14.60666670257187</v>
       </c>
       <c r="C20" t="n">
-        <v>5.80735576570679</v>
+        <v>5.807344733617548</v>
       </c>
       <c r="D20" t="n">
-        <v>-36.99933833628334</v>
+        <v>-36.99934535400175</v>
       </c>
       <c r="E20" t="n">
         <v>-14.06035568342124</v>
@@ -34525,7 +34525,7 @@
         <v>14.4827664797339</v>
       </c>
       <c r="H20" t="n">
-        <v>57.10203864869958</v>
+        <v>57.10205007773608</v>
       </c>
       <c r="I20" t="n">
         <v>19.07969193715464</v>
@@ -34542,7 +34542,7 @@
         <v>5.552070909779561</v>
       </c>
       <c r="D21" t="n">
-        <v>-37.44662565818086</v>
+        <v>-37.4466326019646</v>
       </c>
       <c r="E21" t="n">
         <v>-15.65253283542536</v>
@@ -34554,7 +34554,7 @@
         <v>14.93268079135173</v>
       </c>
       <c r="H21" t="n">
-        <v>58.29782432001966</v>
+        <v>58.29783562608728</v>
       </c>
       <c r="I21" t="n">
         <v>19.98252082265555</v>
@@ -34571,7 +34571,7 @@
         <v>3.376121437455937</v>
       </c>
       <c r="D22" t="n">
-        <v>-37.24372000533128</v>
+        <v>-37.24371308697864</v>
       </c>
       <c r="E22" t="n">
         <v>-18.55594660013272</v>
@@ -34594,13 +34594,13 @@
         <v>44964</v>
       </c>
       <c r="B23" t="n">
-        <v>-11.15268292607744</v>
+        <v>-11.15266764037603</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.933676787602434</v>
+        <v>-1.933685696583631</v>
       </c>
       <c r="D23" t="n">
-        <v>-41.48824295003509</v>
+        <v>-41.48823676523781</v>
       </c>
       <c r="E23" t="n">
         <v>-18.78252908175832</v>
@@ -34609,10 +34609,10 @@
         <v>-50.10111454729574</v>
       </c>
       <c r="G23" t="n">
-        <v>10.60819071963426</v>
+        <v>10.60818362365563</v>
       </c>
       <c r="H23" t="n">
-        <v>58.81801826138557</v>
+        <v>58.81800670352584</v>
       </c>
       <c r="I23" t="n">
         <v>10.7141133146831</v>
@@ -34623,13 +34623,13 @@
         <v>44965</v>
       </c>
       <c r="B24" t="n">
-        <v>-11.56063579001955</v>
+        <v>-11.56063025444067</v>
       </c>
       <c r="C24" t="n">
-        <v>2.855638608305489</v>
+        <v>2.85564838836172</v>
       </c>
       <c r="D24" t="n">
-        <v>-40.21376471890714</v>
+        <v>-40.21375825506007</v>
       </c>
       <c r="E24" t="n">
         <v>-16.45893483922102</v>
@@ -34638,13 +34638,13 @@
         <v>-44.07826973186567</v>
       </c>
       <c r="G24" t="n">
-        <v>11.60952485451092</v>
+        <v>11.60951751266246</v>
       </c>
       <c r="H24" t="n">
-        <v>62.00643790857158</v>
+        <v>62.00644987954136</v>
       </c>
       <c r="I24" t="n">
-        <v>14.28787175168349</v>
+        <v>14.28785881311405</v>
       </c>
     </row>
     <row r="25">
@@ -34652,10 +34652,10 @@
         <v>44966</v>
       </c>
       <c r="B25" t="n">
-        <v>-13.4368577145253</v>
+        <v>-13.43686179603259</v>
       </c>
       <c r="C25" t="n">
-        <v>5.67282573659853</v>
+        <v>5.672815703770717</v>
       </c>
       <c r="D25" t="n">
         <v>-40.08191532584978</v>
@@ -34667,7 +34667,7 @@
         <v>-42.25052729484825</v>
       </c>
       <c r="G25" t="n">
-        <v>11.65067676828095</v>
+        <v>11.65068405892002</v>
       </c>
       <c r="H25" t="n">
         <v>64.69531240252056</v>
@@ -34681,13 +34681,13 @@
         <v>44967</v>
       </c>
       <c r="B26" t="n">
-        <v>-15.32256054574844</v>
+        <v>-15.3225549825181</v>
       </c>
       <c r="C26" t="n">
         <v>4.528935689617386</v>
       </c>
       <c r="D26" t="n">
-        <v>-38.46251411032051</v>
+        <v>-38.46250726377017</v>
       </c>
       <c r="E26" t="n">
         <v>-14.1080861725807</v>
@@ -34696,10 +34696,10 @@
         <v>-43.02512293070519</v>
       </c>
       <c r="G26" t="n">
-        <v>16.29398414152816</v>
+        <v>16.29399199104933</v>
       </c>
       <c r="H26" t="n">
-        <v>66.29553751896557</v>
+        <v>66.295524835542</v>
       </c>
       <c r="I26" t="n">
         <v>26.70599064266366</v>
@@ -34710,7 +34710,7 @@
         <v>44970</v>
       </c>
       <c r="B27" t="n">
-        <v>-18.7038885953311</v>
+        <v>-18.70389204341065</v>
       </c>
       <c r="C27" t="n">
         <v>4.014338103738213</v>
@@ -34725,13 +34725,13 @@
         <v>-44.62854350907771</v>
       </c>
       <c r="G27" t="n">
-        <v>18.97606964477734</v>
+        <v>18.97607771343781</v>
       </c>
       <c r="H27" t="n">
         <v>64.27428054900881</v>
       </c>
       <c r="I27" t="n">
-        <v>24.16112458788589</v>
+        <v>24.16111014012663</v>
       </c>
     </row>
     <row r="28">
@@ -34745,7 +34745,7 @@
         <v>4.651557630877146</v>
       </c>
       <c r="D28" t="n">
-        <v>-40.02900911309823</v>
+        <v>-40.02901565481842</v>
       </c>
       <c r="E28" t="n">
         <v>-12.97818979561633</v>
@@ -34757,7 +34757,7 @@
         <v>17.51991180687484</v>
       </c>
       <c r="H28" t="n">
-        <v>63.90117811405669</v>
+        <v>63.90119045566252</v>
       </c>
       <c r="I28" t="n">
         <v>23.55401646818396</v>
@@ -34768,10 +34768,10 @@
         <v>44972</v>
       </c>
       <c r="B29" t="n">
-        <v>-17.36773070163652</v>
+        <v>-17.36773981046917</v>
       </c>
       <c r="C29" t="n">
-        <v>2.283304051350066</v>
+        <v>2.283313862635117</v>
       </c>
       <c r="D29" t="n">
         <v>-39.92831083700854</v>
@@ -34783,13 +34783,13 @@
         <v>-46.79724550172661</v>
       </c>
       <c r="G29" t="n">
-        <v>15.88130778549979</v>
+        <v>15.88130003172268</v>
       </c>
       <c r="H29" t="n">
-        <v>63.35076848820847</v>
+        <v>63.35075637333281</v>
       </c>
       <c r="I29" t="n">
-        <v>25.48004755579865</v>
+        <v>25.48006186313669</v>
       </c>
     </row>
     <row r="30">
@@ -34797,13 +34797,13 @@
         <v>44973</v>
       </c>
       <c r="B30" t="n">
-        <v>-15.85637380524771</v>
+        <v>-15.8563833041815</v>
       </c>
       <c r="C30" t="n">
         <v>17.12911532618617</v>
       </c>
       <c r="D30" t="n">
-        <v>-37.50402269275101</v>
+        <v>-37.50401568746664</v>
       </c>
       <c r="E30" t="n">
         <v>-14.49816039177078</v>
@@ -34815,10 +34815,10 @@
         <v>17.8995377485418</v>
       </c>
       <c r="H30" t="n">
-        <v>61.91050881232903</v>
+        <v>61.91052081194874</v>
       </c>
       <c r="I30" t="n">
-        <v>27.44100484507495</v>
+        <v>27.44101943364645</v>
       </c>
     </row>
     <row r="31">
@@ -34832,7 +34832,7 @@
         <v>23.91915796979112</v>
       </c>
       <c r="D31" t="n">
-        <v>-33.97506666520363</v>
+        <v>-33.97505887516578</v>
       </c>
       <c r="E31" t="n">
         <v>-10.92405301840568</v>
@@ -34844,10 +34844,10 @@
         <v>25.33967624266196</v>
       </c>
       <c r="H31" t="n">
-        <v>64.25992292563588</v>
+        <v>64.25991032989791</v>
       </c>
       <c r="I31" t="n">
-        <v>31.51450736063446</v>
+        <v>31.51453848876688</v>
       </c>
     </row>
     <row r="32">
@@ -34855,13 +34855,13 @@
         <v>44977</v>
       </c>
       <c r="B32" t="n">
-        <v>-14.87561353925492</v>
+        <v>-14.87561922175242</v>
       </c>
       <c r="C32" t="n">
         <v>19.61811964603284</v>
       </c>
       <c r="D32" t="n">
-        <v>-37.01514377135</v>
+        <v>-37.015150940834</v>
       </c>
       <c r="E32" t="n">
         <v>-12.95767507426349</v>
@@ -34876,7 +34876,7 @@
         <v>59.14170766402243</v>
       </c>
       <c r="I32" t="n">
-        <v>24.45059966536844</v>
+        <v>24.450585554128</v>
       </c>
     </row>
     <row r="33">
@@ -34884,7 +34884,7 @@
         <v>44978</v>
       </c>
       <c r="B33" t="n">
-        <v>-16.09058498817274</v>
+        <v>-16.0905754735894</v>
       </c>
       <c r="C33" t="n">
         <v>20.02054303142249</v>
@@ -34899,7 +34899,7 @@
         <v>-34.84402535312108</v>
       </c>
       <c r="G33" t="n">
-        <v>21.35219118865084</v>
+        <v>21.35219948435621</v>
       </c>
       <c r="H33" t="n">
         <v>58.0193456821104</v>
@@ -34919,7 +34919,7 @@
         <v>14.18458252423589</v>
       </c>
       <c r="D34" t="n">
-        <v>-36.91247477726529</v>
+        <v>-36.91246741722784</v>
       </c>
       <c r="E34" t="n">
         <v>-14.94994446711267</v>
@@ -34934,7 +34934,7 @@
         <v>54.62497605273147</v>
       </c>
       <c r="I34" t="n">
-        <v>26.65201854751447</v>
+        <v>26.65200393262834</v>
       </c>
     </row>
     <row r="35">
@@ -34945,7 +34945,7 @@
         <v>-18.60152164771592</v>
       </c>
       <c r="C35" t="n">
-        <v>19.21701431513336</v>
+        <v>19.2170267597696</v>
       </c>
       <c r="D35" t="n">
         <v>-33.91122858596437</v>
@@ -34974,10 +34974,10 @@
         <v>-18.62598501883454</v>
       </c>
       <c r="C36" t="n">
-        <v>18.62166155611438</v>
+        <v>18.62164897192935</v>
       </c>
       <c r="D36" t="n">
-        <v>-31.52576281197429</v>
+        <v>-31.52576691049362</v>
       </c>
       <c r="E36" t="n">
         <v>-14.58282800965025</v>
@@ -34992,7 +34992,7 @@
         <v>53.76283951658272</v>
       </c>
       <c r="I36" t="n">
-        <v>26.30459001188681</v>
+        <v>26.30460497310276</v>
       </c>
     </row>
     <row r="37">
@@ -35021,7 +35021,7 @@
         <v>48.8738305377163</v>
       </c>
       <c r="I37" t="n">
-        <v>22.93067650229485</v>
+        <v>22.93066214607136</v>
       </c>
     </row>
     <row r="38">
@@ -35029,7 +35029,7 @@
         <v>44985</v>
       </c>
       <c r="B38" t="n">
-        <v>-17.27385493344967</v>
+        <v>-17.27384903171404</v>
       </c>
       <c r="C38" t="n">
         <v>22.6404333023736</v>
@@ -35044,13 +35044,13 @@
         <v>-36.42305522294378</v>
       </c>
       <c r="G38" t="n">
-        <v>17.35207678840634</v>
+        <v>17.35206858810501</v>
       </c>
       <c r="H38" t="n">
-        <v>50.83978675923002</v>
+        <v>50.83979798241343</v>
       </c>
       <c r="I38" t="n">
-        <v>21.36087832593707</v>
+        <v>21.36086421689267</v>
       </c>
     </row>
     <row r="39">
@@ -35061,7 +35061,7 @@
         <v>-9.7078515602394</v>
       </c>
       <c r="C39" t="n">
-        <v>31.97480433287751</v>
+        <v>31.97481230673302</v>
       </c>
       <c r="D39" t="n">
         <v>-27.61200367840709</v>
@@ -35076,7 +35076,7 @@
         <v>21.91018026744151</v>
       </c>
       <c r="H39" t="n">
-        <v>61.49370107804688</v>
+        <v>61.49371391683323</v>
       </c>
       <c r="I39" t="n">
         <v>26.67141341780612</v>
@@ -35087,7 +35087,7 @@
         <v>44987</v>
       </c>
       <c r="B40" t="n">
-        <v>-10.11298508937602</v>
+        <v>-10.11299063059558</v>
       </c>
       <c r="C40" t="n">
         <v>19.9922723562157</v>
@@ -35102,10 +35102,10 @@
         <v>-30.77411532429669</v>
       </c>
       <c r="G40" t="n">
-        <v>20.9177619245789</v>
+        <v>20.91775326947152</v>
       </c>
       <c r="H40" t="n">
-        <v>56.55721767501281</v>
+        <v>56.55722993949202</v>
       </c>
       <c r="I40" t="n">
         <v>20.20511441328614</v>
@@ -35134,7 +35134,7 @@
         <v>19.97297727412279</v>
       </c>
       <c r="H41" t="n">
-        <v>62.05101317652266</v>
+        <v>62.05102614025317</v>
       </c>
       <c r="I41" t="n">
         <v>17.88522183888848</v>
@@ -35145,13 +35145,13 @@
         <v>44991</v>
       </c>
       <c r="B42" t="n">
-        <v>-7.266150668551463</v>
+        <v>-7.266162502800699</v>
       </c>
       <c r="C42" t="n">
         <v>24.28694985541644</v>
       </c>
       <c r="D42" t="n">
-        <v>-30.16130718879553</v>
+        <v>-30.16129920729813</v>
       </c>
       <c r="E42" t="n">
         <v>-19.97601991799662</v>
@@ -35160,7 +35160,7 @@
         <v>-32.43581491059849</v>
       </c>
       <c r="G42" t="n">
-        <v>21.52250729244101</v>
+        <v>21.5225159545213</v>
       </c>
       <c r="H42" t="n">
         <v>64.89360681772109</v>
@@ -35174,7 +35174,7 @@
         <v>44993</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.8804982131239369</v>
+        <v>-0.8804917221198583</v>
       </c>
       <c r="C43" t="n">
         <v>30.04241413851316</v>
@@ -35203,13 +35203,13 @@
         <v>44994</v>
       </c>
       <c r="B44" t="n">
-        <v>-4.919255908811959</v>
+        <v>-4.919249593920927</v>
       </c>
       <c r="C44" t="n">
-        <v>29.52492836354867</v>
+        <v>29.52491383720006</v>
       </c>
       <c r="D44" t="n">
-        <v>-32.00009238650365</v>
+        <v>-32.00010039960694</v>
       </c>
       <c r="E44" t="n">
         <v>-17.33127496973636</v>
@@ -35232,7 +35232,7 @@
         <v>44995</v>
       </c>
       <c r="B45" t="n">
-        <v>-2.670043693754776</v>
+        <v>-2.670037357111332</v>
       </c>
       <c r="C45" t="n">
         <v>31.29346757861284</v>
@@ -35247,13 +35247,13 @@
         <v>-31.83544496946698</v>
       </c>
       <c r="G45" t="n">
-        <v>33.71367202091895</v>
+        <v>33.7136824269769</v>
       </c>
       <c r="H45" t="n">
         <v>79.458663033249</v>
       </c>
       <c r="I45" t="n">
-        <v>26.14400893024353</v>
+        <v>26.14399440155246</v>
       </c>
     </row>
     <row r="46">
@@ -35261,7 +35261,7 @@
         <v>44998</v>
       </c>
       <c r="B46" t="n">
-        <v>-7.290690987649073</v>
+        <v>-7.29070345752959</v>
       </c>
       <c r="C46" t="n">
         <v>29.15084325384258</v>
@@ -35276,10 +35276,10 @@
         <v>-33.58925078370915</v>
       </c>
       <c r="G46" t="n">
-        <v>30.30908432030095</v>
+        <v>30.30909431434516</v>
       </c>
       <c r="H46" t="n">
-        <v>72.07756112625083</v>
+        <v>72.0775455882418</v>
       </c>
       <c r="I46" t="n">
         <v>22.94836451711337</v>
@@ -35308,7 +35308,7 @@
         <v>28.42832520184053</v>
       </c>
       <c r="H47" t="n">
-        <v>59.58053900443488</v>
+        <v>59.58052526548634</v>
       </c>
       <c r="I47" t="n">
         <v>17.08525002537016</v>
@@ -35325,7 +35325,7 @@
         <v>17.02086734345962</v>
       </c>
       <c r="D48" t="n">
-        <v>-31.40650330335744</v>
+        <v>-31.40651143794047</v>
       </c>
       <c r="E48" t="n">
         <v>-19.94314825554189</v>
@@ -35351,10 +35351,10 @@
         <v>-11.90541449199521</v>
       </c>
       <c r="C49" t="n">
-        <v>22.77508891276845</v>
+        <v>22.77507574198827</v>
       </c>
       <c r="D49" t="n">
-        <v>-30.92016986403269</v>
+        <v>-30.92016172817842</v>
       </c>
       <c r="E49" t="n">
         <v>-19.45248824052701</v>
@@ -35366,7 +35366,7 @@
         <v>27.34995686221848</v>
       </c>
       <c r="H49" t="n">
-        <v>60.45066809730437</v>
+        <v>60.45065428250203</v>
       </c>
       <c r="I49" t="n">
         <v>14.45667158637378</v>
@@ -35377,7 +35377,7 @@
         <v>45002</v>
       </c>
       <c r="B50" t="n">
-        <v>-13.59044922897126</v>
+        <v>-13.59044839055706</v>
       </c>
       <c r="C50" t="n">
         <v>29.27328105140488</v>
@@ -35392,7 +35392,7 @@
         <v>-30.769231509302</v>
       </c>
       <c r="G50" t="n">
-        <v>27.31464517094955</v>
+        <v>27.31465444201557</v>
       </c>
       <c r="H50" t="n">
         <v>59.24206111188954</v>
@@ -35409,10 +35409,10 @@
         <v>-15.42275263909398</v>
       </c>
       <c r="C51" t="n">
-        <v>27.27785873176545</v>
+        <v>27.27787261185255</v>
       </c>
       <c r="D51" t="n">
-        <v>-31.97643400314993</v>
+        <v>-31.97644177103526</v>
       </c>
       <c r="E51" t="n">
         <v>-20.44291008044832</v>
@@ -35424,7 +35424,7 @@
         <v>26.498366325885</v>
       </c>
       <c r="H51" t="n">
-        <v>54.96553018421524</v>
+        <v>54.9655173044312</v>
       </c>
       <c r="I51" t="n">
         <v>16.19925276140282</v>
@@ -35438,10 +35438,10 @@
         <v>-16.75592781674719</v>
       </c>
       <c r="C52" t="n">
-        <v>15.983137166722</v>
+        <v>15.98314866577246</v>
       </c>
       <c r="D52" t="n">
-        <v>-34.25272747529156</v>
+        <v>-34.25272018680582</v>
       </c>
       <c r="E52" t="n">
         <v>-19.47331834526688</v>
@@ -35456,7 +35456,7 @@
         <v>51.51195480319131</v>
       </c>
       <c r="I52" t="n">
-        <v>12.95229655576284</v>
+        <v>12.95230837606574</v>
       </c>
     </row>
     <row r="53">
@@ -35479,7 +35479,7 @@
         <v>-34.32282068487901</v>
       </c>
       <c r="G53" t="n">
-        <v>25.41537649839218</v>
+        <v>25.41538542095459</v>
       </c>
       <c r="H53" t="n">
         <v>48.03765044156976</v>
@@ -35499,7 +35499,7 @@
         <v>15.51977831045721</v>
       </c>
       <c r="D54" t="n">
-        <v>-35.6687875971415</v>
+        <v>-35.66879457805805</v>
       </c>
       <c r="E54" t="n">
         <v>-17.62306993008619</v>
@@ -35522,7 +35522,7 @@
         <v>45009</v>
       </c>
       <c r="B55" t="n">
-        <v>-15.0763912285946</v>
+        <v>-15.07638506020167</v>
       </c>
       <c r="C55" t="n">
         <v>12.85898443082509</v>
@@ -35540,10 +35540,10 @@
         <v>23.66558261797545</v>
       </c>
       <c r="H55" t="n">
-        <v>47.98565813849582</v>
+        <v>47.98564622085038</v>
       </c>
       <c r="I55" t="n">
-        <v>1.950605459214061</v>
+        <v>1.950595744863315</v>
       </c>
     </row>
     <row r="56">
@@ -35566,13 +35566,13 @@
         <v>-37.95665823638254</v>
       </c>
       <c r="G56" t="n">
-        <v>23.44512815470852</v>
+        <v>23.44513703972091</v>
       </c>
       <c r="H56" t="n">
         <v>48.50062338662189</v>
       </c>
       <c r="I56" t="n">
-        <v>2.277340963621799</v>
+        <v>2.277331322319887</v>
       </c>
     </row>
     <row r="57">
@@ -35580,13 +35580,13 @@
         <v>45013</v>
       </c>
       <c r="B57" t="n">
-        <v>-20.27135666308896</v>
+        <v>-20.27134569448801</v>
       </c>
       <c r="C57" t="n">
         <v>6.517150174670427</v>
       </c>
       <c r="D57" t="n">
-        <v>-34.67220572525304</v>
+        <v>-34.67219833242028</v>
       </c>
       <c r="E57" t="n">
         <v>-17.96752610010173</v>
@@ -35598,7 +35598,7 @@
         <v>21.97920321770479</v>
       </c>
       <c r="H57" t="n">
-        <v>48.87284969852976</v>
+        <v>48.8728373970472</v>
       </c>
       <c r="I57" t="n">
         <v>1.227357699250997</v>
@@ -35609,7 +35609,7 @@
         <v>45014</v>
       </c>
       <c r="B58" t="n">
-        <v>-19.05067158334044</v>
+        <v>-19.05067656234133</v>
       </c>
       <c r="C58" t="n">
         <v>4.142391266951018</v>
@@ -35624,7 +35624,7 @@
         <v>-36.41439085578239</v>
       </c>
       <c r="G58" t="n">
-        <v>24.20478414861515</v>
+        <v>24.20479317075226</v>
       </c>
       <c r="H58" t="n">
         <v>51.16164250924775</v>
@@ -35667,13 +35667,13 @@
         <v>45019</v>
       </c>
       <c r="B60" t="n">
-        <v>-17.48567624724985</v>
+        <v>-17.4856664035985</v>
       </c>
       <c r="C60" t="n">
         <v>14.68842919215183</v>
       </c>
       <c r="D60" t="n">
-        <v>-31.61805668566483</v>
+        <v>-31.61804878212283</v>
       </c>
       <c r="E60" t="n">
         <v>-11.29153257855178</v>
@@ -35688,7 +35688,7 @@
         <v>52.82481265335437</v>
       </c>
       <c r="I60" t="n">
-        <v>6.475631946649418</v>
+        <v>6.475621720441782</v>
       </c>
     </row>
     <row r="61">
@@ -35696,10 +35696,10 @@
         <v>45021</v>
       </c>
       <c r="B61" t="n">
-        <v>-19.34885723500881</v>
+        <v>-19.34884181076765</v>
       </c>
       <c r="C61" t="n">
-        <v>20.09687982731483</v>
+        <v>20.09686709090648</v>
       </c>
       <c r="D61" t="n">
         <v>-32.87968364243699</v>
@@ -35714,7 +35714,7 @@
         <v>28.9277436270037</v>
       </c>
       <c r="H61" t="n">
-        <v>47.13211596146844</v>
+        <v>47.13210422831011</v>
       </c>
       <c r="I61" t="n">
         <v>8.682665761848551</v>
@@ -35725,13 +35725,13 @@
         <v>45022</v>
       </c>
       <c r="B62" t="n">
-        <v>-18.21685328897849</v>
+        <v>-18.2168377343525</v>
       </c>
       <c r="C62" t="n">
-        <v>24.36674562252921</v>
+        <v>24.36675889868143</v>
       </c>
       <c r="D62" t="n">
-        <v>-32.95227474187059</v>
+        <v>-32.95228235460824</v>
       </c>
       <c r="E62" t="n">
         <v>-12.67063803130704</v>
@@ -35783,13 +35783,13 @@
         <v>45027</v>
       </c>
       <c r="B64" t="n">
-        <v>-18.02589942214645</v>
+        <v>-18.02590525104361</v>
       </c>
       <c r="C64" t="n">
-        <v>13.61411417564049</v>
+        <v>13.61410301133488</v>
       </c>
       <c r="D64" t="n">
-        <v>-32.56338103577472</v>
+        <v>-32.56338852655589</v>
       </c>
       <c r="E64" t="n">
         <v>-15.88764483671978</v>
@@ -35812,13 +35812,13 @@
         <v>45028</v>
       </c>
       <c r="B65" t="n">
-        <v>-18.21924583390756</v>
+        <v>-18.21923643401319</v>
       </c>
       <c r="C65" t="n">
         <v>19.28252542117628</v>
       </c>
       <c r="D65" t="n">
-        <v>-36.88054051448732</v>
+        <v>-36.88053385746252</v>
       </c>
       <c r="E65" t="n">
         <v>-15.49018340516304</v>
@@ -35830,7 +35830,7 @@
         <v>26.23875049577315</v>
       </c>
       <c r="H65" t="n">
-        <v>45.8016652142383</v>
+        <v>45.80165418760669</v>
       </c>
       <c r="I65" t="n">
         <v>3.44891759667858</v>
@@ -35841,10 +35841,10 @@
         <v>45029</v>
       </c>
       <c r="B66" t="n">
-        <v>-17.61593954798493</v>
+        <v>-17.61594530610938</v>
       </c>
       <c r="C66" t="n">
-        <v>22.88924446188723</v>
+        <v>22.8892319542594</v>
       </c>
       <c r="D66" t="n">
         <v>-35.02015203969025</v>
@@ -35859,7 +35859,7 @@
         <v>23.47126146549181</v>
       </c>
       <c r="H66" t="n">
-        <v>46.9922209646493</v>
+        <v>46.99223219814739</v>
       </c>
       <c r="I66" t="n">
         <v>2.630916019968432</v>
@@ -35876,7 +35876,7 @@
         <v>18.19502892780256</v>
       </c>
       <c r="D67" t="n">
-        <v>-33.69652011281428</v>
+        <v>-33.69652738029185</v>
       </c>
       <c r="E67" t="n">
         <v>-15.92903494350202</v>
@@ -35885,13 +35885,13 @@
         <v>-34.60605968128551</v>
       </c>
       <c r="G67" t="n">
-        <v>22.78115289082163</v>
+        <v>22.78116144230844</v>
       </c>
       <c r="H67" t="n">
         <v>46.87294875605894</v>
       </c>
       <c r="I67" t="n">
-        <v>4.358495324824485</v>
+        <v>4.358485543758617</v>
       </c>
     </row>
     <row r="68">
@@ -35905,7 +35905,7 @@
         <v>19.19994618847545</v>
       </c>
       <c r="D68" t="n">
-        <v>-33.45363826736411</v>
+        <v>-33.45364554133607</v>
       </c>
       <c r="E68" t="n">
         <v>-15.4223684334489</v>
@@ -35914,10 +35914,10 @@
         <v>-36.0911291823878</v>
       </c>
       <c r="G68" t="n">
-        <v>22.62655547633416</v>
+        <v>22.62656399629343</v>
       </c>
       <c r="H68" t="n">
-        <v>41.94385386979853</v>
+        <v>41.94384339597192</v>
       </c>
       <c r="I68" t="n">
         <v>7.316638278006016</v>
@@ -35928,7 +35928,7 @@
         <v>45035</v>
       </c>
       <c r="B69" t="n">
-        <v>-21.65792014085915</v>
+        <v>-21.65792567360015</v>
       </c>
       <c r="C69" t="n">
         <v>24.57637019650605</v>
@@ -35957,13 +35957,13 @@
         <v>45036</v>
       </c>
       <c r="B70" t="n">
-        <v>-20.32180578770618</v>
+        <v>-20.321802426139</v>
       </c>
       <c r="C70" t="n">
         <v>29.09584605854447</v>
       </c>
       <c r="D70" t="n">
-        <v>-31.23752375951127</v>
+        <v>-31.23753149833604</v>
       </c>
       <c r="E70" t="n">
         <v>-14.83356585816891</v>
@@ -35986,13 +35986,13 @@
         <v>45037</v>
       </c>
       <c r="B71" t="n">
-        <v>-22.21718932592427</v>
+        <v>-22.21718373243616</v>
       </c>
       <c r="C71" t="n">
         <v>24.62367801432994</v>
       </c>
       <c r="D71" t="n">
-        <v>-33.84422372658705</v>
+        <v>-33.84423102949543</v>
       </c>
       <c r="E71" t="n">
         <v>-15.52225708666685</v>
@@ -36001,7 +36001,7 @@
         <v>-33.19428102778764</v>
       </c>
       <c r="G71" t="n">
-        <v>27.41752847247863</v>
+        <v>27.41751926795843</v>
       </c>
       <c r="H71" t="n">
         <v>41.4570032178073</v>
@@ -36015,7 +36015,7 @@
         <v>45040</v>
       </c>
       <c r="B72" t="n">
-        <v>-19.51327012082694</v>
+        <v>-19.5132736159526</v>
       </c>
       <c r="C72" t="n">
         <v>18.94235050409547</v>
@@ -36033,10 +36033,10 @@
         <v>29.86125933519011</v>
       </c>
       <c r="H72" t="n">
-        <v>39.58447058476111</v>
+        <v>39.58446048180952</v>
       </c>
       <c r="I72" t="n">
-        <v>13.23828094241737</v>
+        <v>13.23826959825487</v>
       </c>
     </row>
     <row r="73">
@@ -36044,7 +36044,7 @@
         <v>45041</v>
       </c>
       <c r="B73" t="n">
-        <v>-15.5774342190828</v>
+        <v>-15.57743515486935</v>
       </c>
       <c r="C73" t="n">
         <v>12.60045671020504</v>
@@ -36062,7 +36062,7 @@
         <v>33.47424658143068</v>
       </c>
       <c r="H73" t="n">
-        <v>40.08359270090595</v>
+        <v>40.08358254323608</v>
       </c>
       <c r="I73" t="n">
         <v>10.75872260467268</v>
@@ -36079,7 +36079,7 @@
         <v>14.28718845525012</v>
       </c>
       <c r="D74" t="n">
-        <v>-32.8593519320597</v>
+        <v>-32.8593597137336</v>
       </c>
       <c r="E74" t="n">
         <v>-14.62957344452325</v>
@@ -36105,7 +36105,7 @@
         <v>-22.8734463826578</v>
       </c>
       <c r="C75" t="n">
-        <v>19.76553693698866</v>
+        <v>19.76554810143705</v>
       </c>
       <c r="D75" t="n">
         <v>-32.93522100021815</v>
@@ -36123,7 +36123,7 @@
         <v>35.73261378763198</v>
       </c>
       <c r="I75" t="n">
-        <v>7.619234003335817</v>
+        <v>7.619244262207259</v>
       </c>
     </row>
     <row r="76">
@@ -36137,7 +36137,7 @@
         <v>20.60235583248156</v>
       </c>
       <c r="D76" t="n">
-        <v>-32.14496306191151</v>
+        <v>-32.14495533922771</v>
       </c>
       <c r="E76" t="n">
         <v>-12.82996721037294</v>
@@ -36163,10 +36163,10 @@
         <v>-22.01101004894436</v>
       </c>
       <c r="C77" t="n">
-        <v>23.61108055592947</v>
+        <v>23.61109207885637</v>
       </c>
       <c r="D77" t="n">
-        <v>-32.51455059614623</v>
+        <v>-32.51455825121081</v>
       </c>
       <c r="E77" t="n">
         <v>-11.11250512017831</v>
@@ -36178,10 +36178,10 @@
         <v>45.71365133615044</v>
       </c>
       <c r="H77" t="n">
-        <v>38.26993186907828</v>
+        <v>38.2699415458752</v>
       </c>
       <c r="I77" t="n">
-        <v>13.78189950026183</v>
+        <v>13.78188823013884</v>
       </c>
     </row>
     <row r="78">
@@ -36195,7 +36195,7 @@
         <v>23.7659816837569</v>
       </c>
       <c r="D78" t="n">
-        <v>-32.95861475128869</v>
+        <v>-32.95862230814943</v>
       </c>
       <c r="E78" t="n">
         <v>-12.12214872967794</v>
@@ -36210,7 +36210,7 @@
         <v>32.75446750139701</v>
       </c>
       <c r="I78" t="n">
-        <v>8.733579120790624</v>
+        <v>8.733568707506191</v>
       </c>
     </row>
     <row r="79">
@@ -36218,10 +36218,10 @@
         <v>45050</v>
       </c>
       <c r="B79" t="n">
-        <v>-24.83509260837413</v>
+        <v>-24.83509786564334</v>
       </c>
       <c r="C79" t="n">
-        <v>27.86268925181292</v>
+        <v>27.86270156910704</v>
       </c>
       <c r="D79" t="n">
         <v>-32.80320317355864</v>
@@ -36233,13 +36233,13 @@
         <v>-13.38167663818997</v>
       </c>
       <c r="G79" t="n">
-        <v>42.33817884306499</v>
+        <v>42.33816804720085</v>
       </c>
       <c r="H79" t="n">
         <v>34.25072682673238</v>
       </c>
       <c r="I79" t="n">
-        <v>14.81161336452039</v>
+        <v>14.81160187682717</v>
       </c>
     </row>
     <row r="80">
@@ -36247,10 +36247,10 @@
         <v>45051</v>
       </c>
       <c r="B80" t="n">
-        <v>-25.75365592750416</v>
+        <v>-25.75366364597215</v>
       </c>
       <c r="C80" t="n">
-        <v>52.42343841801713</v>
+        <v>52.42345300565327</v>
       </c>
       <c r="D80" t="n">
         <v>-33.83920034534022</v>
@@ -36262,10 +36262,10 @@
         <v>-11.44210849402154</v>
       </c>
       <c r="G80" t="n">
-        <v>40.05793312565282</v>
+        <v>40.05792276348328</v>
       </c>
       <c r="H80" t="n">
-        <v>32.58130854178334</v>
+        <v>32.58131763044514</v>
       </c>
       <c r="I80" t="n">
         <v>15.70915136466104</v>
@@ -36276,7 +36276,7 @@
         <v>45054</v>
       </c>
       <c r="B81" t="n">
-        <v>-24.14230044000153</v>
+        <v>-24.14229513532702</v>
       </c>
       <c r="C81" t="n">
         <v>69.82475637190866</v>
@@ -36294,7 +36294,7 @@
         <v>41.39293542435327</v>
       </c>
       <c r="H81" t="n">
-        <v>34.95326384631667</v>
+        <v>34.95327310560674</v>
       </c>
       <c r="I81" t="n">
         <v>15.84254244115453</v>
@@ -36305,7 +36305,7 @@
         <v>45055</v>
       </c>
       <c r="B82" t="n">
-        <v>-25.04685667872282</v>
+        <v>-25.04685930544856</v>
       </c>
       <c r="C82" t="n">
         <v>76.04511550454663</v>
@@ -36323,7 +36323,7 @@
         <v>43.18709954376827</v>
       </c>
       <c r="H82" t="n">
-        <v>36.55979596031023</v>
+        <v>36.55978658316768</v>
       </c>
       <c r="I82" t="n">
         <v>17.56039485886303</v>
@@ -36334,7 +36334,7 @@
         <v>45056</v>
       </c>
       <c r="B83" t="n">
-        <v>-23.86634974339055</v>
+        <v>-23.86635792181169</v>
       </c>
       <c r="C83" t="n">
         <v>88.79787173407989</v>
@@ -36355,7 +36355,7 @@
         <v>40.76848515981744</v>
       </c>
       <c r="I83" t="n">
-        <v>18.86918849609671</v>
+        <v>18.86917648722779</v>
       </c>
     </row>
     <row r="84">
@@ -36384,7 +36384,7 @@
         <v>40.60437121069942</v>
       </c>
       <c r="I84" t="n">
-        <v>21.49652425118081</v>
+        <v>21.49651196777065</v>
       </c>
     </row>
     <row r="85">
@@ -36407,10 +36407,10 @@
         <v>3.4710718580514</v>
       </c>
       <c r="G85" t="n">
-        <v>38.65104100599142</v>
+        <v>38.65103013588356</v>
       </c>
       <c r="H85" t="n">
-        <v>44.20826733142795</v>
+        <v>44.20827753842107</v>
       </c>
       <c r="I85" t="n">
         <v>29.73433558136196</v>
@@ -36424,7 +36424,7 @@
         <v>-19.39181455314486</v>
       </c>
       <c r="C86" t="n">
-        <v>85.0791916573894</v>
+        <v>85.07917229605151</v>
       </c>
       <c r="D86" t="n">
         <v>-23.1384212075596</v>
@@ -36439,7 +36439,7 @@
         <v>40.80518468398238</v>
       </c>
       <c r="H86" t="n">
-        <v>45.06925089133167</v>
+        <v>45.06924064002889</v>
       </c>
       <c r="I86" t="n">
         <v>37.0571456743449</v>
@@ -36453,7 +36453,7 @@
         <v>-18.8783547929949</v>
       </c>
       <c r="C87" t="n">
-        <v>93.89767100492665</v>
+        <v>93.89769147521162</v>
       </c>
       <c r="D87" t="n">
         <v>-20.815590914765</v>
@@ -36465,10 +36465,10 @@
         <v>20.11439291439448</v>
       </c>
       <c r="G87" t="n">
-        <v>40.28553313295782</v>
+        <v>40.28554423038708</v>
       </c>
       <c r="H87" t="n">
-        <v>43.5659039056097</v>
+        <v>43.56589368117027</v>
       </c>
       <c r="I87" t="n">
         <v>41.65856106199703</v>
@@ -36479,13 +36479,13 @@
         <v>45063</v>
       </c>
       <c r="B88" t="n">
-        <v>-18.8914227913757</v>
+        <v>-18.89143203659397</v>
       </c>
       <c r="C88" t="n">
         <v>99.03246669588898</v>
       </c>
       <c r="D88" t="n">
-        <v>-15.63753923850449</v>
+        <v>-15.63753336222166</v>
       </c>
       <c r="E88" t="n">
         <v>1.811539985164567</v>
@@ -36529,7 +36529,7 @@
         <v>45.41971551856445</v>
       </c>
       <c r="I89" t="n">
-        <v>47.62660550286291</v>
+        <v>47.62659655269752</v>
       </c>
     </row>
     <row r="90">
@@ -36540,7 +36540,7 @@
         <v>-18.1824649464718</v>
       </c>
       <c r="C90" t="n">
-        <v>136.1211273249051</v>
+        <v>136.1211128453174</v>
       </c>
       <c r="D90" t="n">
         <v>-9.920805196746297</v>
@@ -36552,13 +36552,13 @@
         <v>13.45646742516853</v>
       </c>
       <c r="G90" t="n">
-        <v>44.54843121428939</v>
+        <v>44.54844319626785</v>
       </c>
       <c r="H90" t="n">
-        <v>43.14745139325571</v>
+        <v>43.14746157471374</v>
       </c>
       <c r="I90" t="n">
-        <v>44.83390677030141</v>
+        <v>44.83392397209496</v>
       </c>
     </row>
     <row r="91">
@@ -36572,7 +36572,7 @@
         <v>148.2698002141272</v>
       </c>
       <c r="D91" t="n">
-        <v>-3.280632807308614</v>
+        <v>-3.280639884700398</v>
       </c>
       <c r="E91" t="n">
         <v>-3.819044572476604</v>
@@ -36584,7 +36584,7 @@
         <v>45.50429646379237</v>
       </c>
       <c r="H91" t="n">
-        <v>41.52870143488789</v>
+        <v>41.52869152289962</v>
       </c>
       <c r="I91" t="n">
         <v>44.14082842093207</v>
@@ -36595,13 +36595,13 @@
         <v>45069</v>
       </c>
       <c r="B92" t="n">
-        <v>-18.25820847922664</v>
+        <v>-18.25819385519139</v>
       </c>
       <c r="C92" t="n">
-        <v>137.9470197320336</v>
+        <v>137.947034486864</v>
       </c>
       <c r="D92" t="n">
-        <v>-6.068782181485844</v>
+        <v>-6.068788766848177</v>
       </c>
       <c r="E92" t="n">
         <v>-6.126607843262921</v>
@@ -36627,10 +36627,10 @@
         <v>-20.39881068768235</v>
       </c>
       <c r="C93" t="n">
-        <v>146.88066454028</v>
+        <v>146.8806483712977</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3346809125640782</v>
+        <v>0.3346879161523875</v>
       </c>
       <c r="E93" t="n">
         <v>-6.40002174847476</v>
@@ -36642,7 +36642,7 @@
         <v>40.73977366347519</v>
       </c>
       <c r="H93" t="n">
-        <v>41.1095047662722</v>
+        <v>41.10949499131016</v>
       </c>
       <c r="I93" t="n">
         <v>38.25093075255233</v>
@@ -36653,7 +36653,7 @@
         <v>45071</v>
       </c>
       <c r="B94" t="n">
-        <v>-20.29806887992732</v>
+        <v>-20.29807441737972</v>
       </c>
       <c r="C94" t="n">
         <v>150.4178221113704</v>
@@ -36671,10 +36671,10 @@
         <v>44.25098360170787</v>
       </c>
       <c r="H94" t="n">
-        <v>46.26646505759342</v>
+        <v>46.26645457236928</v>
       </c>
       <c r="I94" t="n">
-        <v>46.53835894569121</v>
+        <v>46.53834161953274</v>
       </c>
     </row>
     <row r="95">
@@ -36682,7 +36682,7 @@
         <v>45072</v>
       </c>
       <c r="B95" t="n">
-        <v>-20.29114837445467</v>
+        <v>-20.29113957988702</v>
       </c>
       <c r="C95" t="n">
         <v>153.8086611104498</v>
@@ -36697,7 +36697,7 @@
         <v>15.84840806865324</v>
       </c>
       <c r="G95" t="n">
-        <v>39.54781920636692</v>
+        <v>39.5478302306985</v>
       </c>
       <c r="H95" t="n">
         <v>43.28014873105887</v>
@@ -36711,13 +36711,13 @@
         <v>45075</v>
       </c>
       <c r="B96" t="n">
-        <v>-18.93015912139414</v>
+        <v>-18.93014449010967</v>
       </c>
       <c r="C96" t="n">
         <v>155.0206231611852</v>
       </c>
       <c r="D96" t="n">
-        <v>5.985759915697764</v>
+        <v>5.985752527139354</v>
       </c>
       <c r="E96" t="n">
         <v>-1.980919585172025</v>
@@ -36729,7 +36729,7 @@
         <v>37.03356968384075</v>
       </c>
       <c r="H96" t="n">
-        <v>42.66483672041983</v>
+        <v>42.66484630304353</v>
       </c>
       <c r="I96" t="n">
         <v>44.57535348371431</v>
@@ -36755,10 +36755,10 @@
         <v>2.925329661513287</v>
       </c>
       <c r="G97" t="n">
-        <v>37.6813065522206</v>
+        <v>37.68131732074869</v>
       </c>
       <c r="H97" t="n">
-        <v>41.73765149897355</v>
+        <v>41.73766096954941</v>
       </c>
       <c r="I97" t="n">
         <v>45.05449184756076</v>
@@ -36798,13 +36798,13 @@
         <v>45078</v>
       </c>
       <c r="B99" t="n">
-        <v>-18.46467965565757</v>
+        <v>-18.46467053163623</v>
       </c>
       <c r="C99" t="n">
         <v>174.8430541099076</v>
       </c>
       <c r="D99" t="n">
-        <v>16.25383609419671</v>
+        <v>16.25382764237004</v>
       </c>
       <c r="E99" t="n">
         <v>-2.139793704257109</v>
@@ -36813,7 +36813,7 @@
         <v>12.40694142373082</v>
       </c>
       <c r="G99" t="n">
-        <v>42.92115180520169</v>
+        <v>42.92116342474613</v>
       </c>
       <c r="H99" t="n">
         <v>43.29912227389552</v>
@@ -36827,13 +36827,13 @@
         <v>45079</v>
       </c>
       <c r="B100" t="n">
-        <v>-17.39952610518784</v>
+        <v>-17.3995168201315</v>
       </c>
       <c r="C100" t="n">
-        <v>172.141851226215</v>
+        <v>172.1418708299414</v>
       </c>
       <c r="D100" t="n">
-        <v>15.99063825357225</v>
+        <v>15.99064654699953</v>
       </c>
       <c r="E100" t="n">
         <v>-2.275966013458697</v>
@@ -36845,7 +36845,7 @@
         <v>41.4213454094158</v>
       </c>
       <c r="H100" t="n">
-        <v>42.21812774696409</v>
+        <v>42.21813718980696</v>
       </c>
       <c r="I100" t="n">
         <v>49.71674264353669</v>
@@ -36856,7 +36856,7 @@
         <v>45082</v>
       </c>
       <c r="B101" t="n">
-        <v>-18.0179850573181</v>
+        <v>-18.01799422987028</v>
       </c>
       <c r="C101" t="n">
         <v>156.7079129207885</v>
@@ -36871,10 +36871,10 @@
         <v>0.2814875997915189</v>
       </c>
       <c r="G101" t="n">
-        <v>38.32363698412549</v>
+        <v>38.32362639041646</v>
       </c>
       <c r="H101" t="n">
-        <v>41.20078113434822</v>
+        <v>41.20079008236119</v>
       </c>
       <c r="I101" t="n">
         <v>43.12279638185323</v>
@@ -36885,7 +36885,7 @@
         <v>45083</v>
       </c>
       <c r="B102" t="n">
-        <v>-15.56131661055155</v>
+        <v>-15.56132223011834</v>
       </c>
       <c r="C102" t="n">
         <v>161.6820780609537</v>
@@ -36914,10 +36914,10 @@
         <v>45084</v>
       </c>
       <c r="B103" t="n">
-        <v>-15.67046938043889</v>
+        <v>-15.67048449544585</v>
       </c>
       <c r="C103" t="n">
-        <v>158.5703844990015</v>
+        <v>158.5704020146525</v>
       </c>
       <c r="D103" t="n">
         <v>0.8296034298771904</v>
@@ -36972,7 +36972,7 @@
         <v>45086</v>
       </c>
       <c r="B105" t="n">
-        <v>-13.86714562403707</v>
+        <v>-13.86714980937539</v>
       </c>
       <c r="C105" t="n">
         <v>152.9632953500671</v>
@@ -37001,13 +37001,13 @@
         <v>45089</v>
       </c>
       <c r="B106" t="n">
-        <v>-14.0161358163355</v>
+        <v>-14.01613003868714</v>
       </c>
       <c r="C106" t="n">
         <v>148.8792470261734</v>
       </c>
       <c r="D106" t="n">
-        <v>14.11825216109845</v>
+        <v>14.11825976903569</v>
       </c>
       <c r="E106" t="n">
         <v>-2.820807220195465</v>
@@ -37016,10 +37016,10 @@
         <v>11.51644527415776</v>
       </c>
       <c r="G106" t="n">
-        <v>44.48941259677832</v>
+        <v>44.48942380202134</v>
       </c>
       <c r="H106" t="n">
-        <v>34.71064659310485</v>
+        <v>34.71063836621964</v>
       </c>
       <c r="I106" t="n">
         <v>44.62056839929724</v>
@@ -37030,13 +37030,13 @@
         <v>45090</v>
       </c>
       <c r="B107" t="n">
-        <v>-13.6273325441435</v>
+        <v>-13.6273425242933</v>
       </c>
       <c r="C107" t="n">
-        <v>150.019677848503</v>
+        <v>150.0196947522984</v>
       </c>
       <c r="D107" t="n">
-        <v>19.36491772573441</v>
+        <v>19.36490965451167</v>
       </c>
       <c r="E107" t="n">
         <v>-1.309470831231785</v>
@@ -37048,7 +37048,7 @@
         <v>50.02359988802658</v>
       </c>
       <c r="H107" t="n">
-        <v>33.05838149885625</v>
+        <v>33.05839764793024</v>
       </c>
       <c r="I107" t="n">
         <v>55.60936872903848</v>
@@ -37059,13 +37059,13 @@
         <v>45091</v>
       </c>
       <c r="B108" t="n">
-        <v>-13.14212884987477</v>
+        <v>-13.14211880026519</v>
       </c>
       <c r="C108" t="n">
         <v>181.5867608587544</v>
       </c>
       <c r="D108" t="n">
-        <v>21.77669391306478</v>
+        <v>21.77668562227004</v>
       </c>
       <c r="E108" t="n">
         <v>-0.9239398189491599</v>
@@ -37103,10 +37103,10 @@
         <v>9.315868719325548</v>
       </c>
       <c r="G109" t="n">
-        <v>49.93032430556956</v>
+        <v>49.93033626150696</v>
       </c>
       <c r="H109" t="n">
-        <v>34.62835401055035</v>
+        <v>34.62834586067447</v>
       </c>
       <c r="I109" t="n">
         <v>55.64008919772301</v>
@@ -37117,7 +37117,7 @@
         <v>45093</v>
       </c>
       <c r="B110" t="n">
-        <v>-13.10994902519582</v>
+        <v>-13.1099548105555</v>
       </c>
       <c r="C110" t="n">
         <v>178.2535128491353</v>
@@ -37135,7 +37135,7 @@
         <v>51.2276370421413</v>
       </c>
       <c r="H110" t="n">
-        <v>36.82723502997229</v>
+        <v>36.82724338168488</v>
       </c>
       <c r="I110" t="n">
         <v>54.20554241428566</v>
@@ -37161,10 +37161,10 @@
         <v>12.37036810980903</v>
       </c>
       <c r="G111" t="n">
-        <v>56.43440328533407</v>
+        <v>56.43439029736246</v>
       </c>
       <c r="H111" t="n">
-        <v>41.08344269334043</v>
+        <v>41.08345158094831</v>
       </c>
       <c r="I111" t="n">
         <v>57.45288583586338</v>
@@ -37175,10 +37175,10 @@
         <v>45097</v>
       </c>
       <c r="B112" t="n">
-        <v>-13.13265713838013</v>
+        <v>-13.13266297650482</v>
       </c>
       <c r="C112" t="n">
-        <v>194.7452283309299</v>
+        <v>194.7452055061844</v>
       </c>
       <c r="D112" t="n">
         <v>33.04750233900165</v>
@@ -37190,10 +37190,10 @@
         <v>8.357140677315854</v>
       </c>
       <c r="G112" t="n">
-        <v>56.18450417202716</v>
+        <v>56.18451703347669</v>
       </c>
       <c r="H112" t="n">
-        <v>38.40947105414693</v>
+        <v>38.40946246287664</v>
       </c>
       <c r="I112" t="n">
         <v>61.01530401200663</v>
@@ -37233,13 +37233,13 @@
         <v>45099</v>
       </c>
       <c r="B114" t="n">
-        <v>-12.11468001440106</v>
+        <v>-12.1146740870624</v>
       </c>
       <c r="C114" t="n">
-        <v>191.3441291927024</v>
+        <v>191.3441519212334</v>
       </c>
       <c r="D114" t="n">
-        <v>32.78658724084229</v>
+        <v>32.78659693496173</v>
       </c>
       <c r="E114" t="n">
         <v>3.517889568567334</v>
@@ -37251,7 +37251,7 @@
         <v>60.2194802916022</v>
       </c>
       <c r="H114" t="n">
-        <v>38.55328443090651</v>
+        <v>38.55329315087805</v>
       </c>
       <c r="I114" t="n">
         <v>58.91797446513505</v>
@@ -37320,13 +37320,13 @@
         <v>45104</v>
       </c>
       <c r="B117" t="n">
-        <v>-14.26723110319399</v>
+        <v>-14.26722518153727</v>
       </c>
       <c r="C117" t="n">
         <v>190.2882002043212</v>
       </c>
       <c r="D117" t="n">
-        <v>26.89546722566028</v>
+        <v>26.89547619160333</v>
       </c>
       <c r="E117" t="n">
         <v>10.01690681868583</v>
@@ -37349,13 +37349,13 @@
         <v>45105</v>
       </c>
       <c r="B118" t="n">
-        <v>-12.11996211894075</v>
+        <v>-12.11996284497818</v>
       </c>
       <c r="C118" t="n">
-        <v>204.905805731004</v>
+        <v>204.9058308907751</v>
       </c>
       <c r="D118" t="n">
-        <v>29.66751628186874</v>
+        <v>29.66752570594924</v>
       </c>
       <c r="E118" t="n">
         <v>13.68910139922088</v>
@@ -37364,10 +37364,10 @@
         <v>10.79882132623484</v>
       </c>
       <c r="G118" t="n">
-        <v>65.84676705894417</v>
+        <v>65.84675279320599</v>
       </c>
       <c r="H118" t="n">
-        <v>43.24800916673006</v>
+        <v>43.24799995472712</v>
       </c>
       <c r="I118" t="n">
         <v>73.57967674638716</v>
@@ -37378,10 +37378,10 @@
         <v>45107</v>
       </c>
       <c r="B119" t="n">
-        <v>-13.23668989730719</v>
+        <v>-13.2367060624589</v>
       </c>
       <c r="C119" t="n">
-        <v>202.7747509200105</v>
+        <v>202.7747261880636</v>
       </c>
       <c r="D119" t="n">
         <v>29.44821346991007</v>
@@ -37407,7 +37407,7 @@
         <v>45110</v>
       </c>
       <c r="B120" t="n">
-        <v>-13.01592402591255</v>
+        <v>-13.01590789485615</v>
       </c>
       <c r="C120" t="n">
         <v>200.0318545347367</v>
@@ -37439,10 +37439,10 @@
         <v>-13.96130057026534</v>
       </c>
       <c r="C121" t="n">
-        <v>175.6737734597426</v>
+        <v>175.6737524568554</v>
       </c>
       <c r="D121" t="n">
-        <v>19.91854842415124</v>
+        <v>19.91854035685954</v>
       </c>
       <c r="E121" t="n">
         <v>13.16082381808537</v>
@@ -37454,7 +37454,7 @@
         <v>62.35033490444499</v>
       </c>
       <c r="H121" t="n">
-        <v>36.64305512493089</v>
+        <v>36.6430710940796</v>
       </c>
       <c r="I121" t="n">
         <v>65.75187642173719</v>
@@ -37465,7 +37465,7 @@
         <v>45112</v>
       </c>
       <c r="B122" t="n">
-        <v>-14.43609191046189</v>
+        <v>-14.4360861049844</v>
       </c>
       <c r="C122" t="n">
         <v>172.919297853699</v>
@@ -37494,13 +37494,13 @@
         <v>45113</v>
       </c>
       <c r="B123" t="n">
-        <v>-15.53879279954942</v>
+        <v>-15.53880821438512</v>
       </c>
       <c r="C123" t="n">
-        <v>180.4885067397659</v>
+        <v>180.4885282234777</v>
       </c>
       <c r="D123" t="n">
-        <v>16.76618481786667</v>
+        <v>16.76619264135366</v>
       </c>
       <c r="E123" t="n">
         <v>10.7582875653073</v>
@@ -37512,7 +37512,7 @@
         <v>62.83149349240637</v>
       </c>
       <c r="H123" t="n">
-        <v>40.73736131211905</v>
+        <v>40.73737732998342</v>
       </c>
       <c r="I123" t="n">
         <v>58.3844478184107</v>
@@ -37526,7 +37526,7 @@
         <v>-15.14173731699905</v>
       </c>
       <c r="C124" t="n">
-        <v>187.0833081175934</v>
+        <v>187.0833304200897</v>
       </c>
       <c r="D124" t="n">
         <v>18.77505807640598</v>
@@ -37541,7 +37541,7 @@
         <v>59.19886613950065</v>
       </c>
       <c r="H124" t="n">
-        <v>44.55059786246027</v>
+        <v>44.55058113067074</v>
       </c>
       <c r="I124" t="n">
         <v>58.76307179820024</v>
@@ -37552,13 +37552,13 @@
         <v>45117</v>
       </c>
       <c r="B125" t="n">
-        <v>-16.76128172072728</v>
+        <v>-16.7612912111592</v>
       </c>
       <c r="C125" t="n">
         <v>211.2965387027858</v>
       </c>
       <c r="D125" t="n">
-        <v>17.93824274178943</v>
+        <v>17.93823471846481</v>
       </c>
       <c r="E125" t="n">
         <v>11.18258800949834</v>
@@ -37567,7 +37567,7 @@
         <v>33.21460555487845</v>
       </c>
       <c r="G125" t="n">
-        <v>57.10846457721775</v>
+        <v>57.10845186598667</v>
       </c>
       <c r="H125" t="n">
         <v>41.53377328828811</v>
@@ -37581,10 +37581,10 @@
         <v>45118</v>
       </c>
       <c r="B126" t="n">
-        <v>-17.19681166484127</v>
+        <v>-17.19682111651987</v>
       </c>
       <c r="C126" t="n">
-        <v>206.1101731212097</v>
+        <v>206.1101493697937</v>
       </c>
       <c r="D126" t="n">
         <v>22.19837795568309</v>
@@ -37599,7 +37599,7 @@
         <v>58.45225206200004</v>
       </c>
       <c r="H126" t="n">
-        <v>45.29959069401124</v>
+        <v>45.29957384546863</v>
       </c>
       <c r="I126" t="n">
         <v>51.63112883941956</v>
@@ -37610,13 +37610,13 @@
         <v>45119</v>
       </c>
       <c r="B127" t="n">
-        <v>-16.2593718695014</v>
+        <v>-16.25938150183167</v>
       </c>
       <c r="C127" t="n">
-        <v>212.9428392680224</v>
+        <v>212.9428146845167</v>
       </c>
       <c r="D127" t="n">
-        <v>23.09183900439762</v>
+        <v>23.09183046167227</v>
       </c>
       <c r="E127" t="n">
         <v>4.597354985046165</v>
@@ -37645,7 +37645,7 @@
         <v>201.774759139831</v>
       </c>
       <c r="D128" t="n">
-        <v>17.20302399211098</v>
+        <v>17.20303180665972</v>
       </c>
       <c r="E128" t="n">
         <v>0.7819067073773667</v>
@@ -37654,10 +37654,10 @@
         <v>37.626504419083</v>
       </c>
       <c r="G128" t="n">
-        <v>59.46577525127255</v>
+        <v>59.46578828588398</v>
       </c>
       <c r="H128" t="n">
-        <v>43.31017970931481</v>
+        <v>43.31019612632016</v>
       </c>
       <c r="I128" t="n">
         <v>42.35916099181954</v>
@@ -37668,7 +37668,7 @@
         <v>45121</v>
       </c>
       <c r="B129" t="n">
-        <v>-17.60656272704317</v>
+        <v>-17.60655333840102</v>
       </c>
       <c r="C129" t="n">
         <v>200.571810645821</v>
@@ -37700,7 +37700,7 @@
         <v>-16.06924216763041</v>
       </c>
       <c r="C130" t="n">
-        <v>216.2503255711426</v>
+        <v>216.2503012302509</v>
       </c>
       <c r="D130" t="n">
         <v>18.52716298002006</v>
@@ -37712,10 +37712,10 @@
         <v>46.25912890829837</v>
       </c>
       <c r="G130" t="n">
-        <v>48.17716297217205</v>
+        <v>48.1771518027069</v>
       </c>
       <c r="H130" t="n">
-        <v>38.34544839417169</v>
+        <v>38.34546383630774</v>
       </c>
       <c r="I130" t="n">
         <v>40.90024074120391</v>
@@ -37770,7 +37770,7 @@
         <v>31.61017207776087</v>
       </c>
       <c r="G132" t="n">
-        <v>52.74919523630348</v>
+        <v>52.74920698503869</v>
       </c>
       <c r="H132" t="n">
         <v>37.49649501577726</v>
@@ -37813,13 +37813,13 @@
         <v>45128</v>
       </c>
       <c r="B134" t="n">
-        <v>-17.80200501367793</v>
+        <v>-17.80201441495145</v>
       </c>
       <c r="C134" t="n">
-        <v>228.3349844711908</v>
+        <v>228.3350100854769</v>
       </c>
       <c r="D134" t="n">
-        <v>12.95576933224518</v>
+        <v>12.95577680141005</v>
       </c>
       <c r="E134" t="n">
         <v>-6.348016874151618</v>
@@ -37828,7 +37828,7 @@
         <v>44.29470053907531</v>
       </c>
       <c r="G134" t="n">
-        <v>59.1209205241739</v>
+        <v>59.1209328194961</v>
       </c>
       <c r="H134" t="n">
         <v>34.72765133565782</v>
@@ -37871,13 +37871,13 @@
         <v>45132</v>
       </c>
       <c r="B136" t="n">
-        <v>-12.53855954211573</v>
+        <v>-12.53856948234922</v>
       </c>
       <c r="C136" t="n">
-        <v>234.8925752233966</v>
+        <v>234.8925500068031</v>
       </c>
       <c r="D136" t="n">
-        <v>7.962363855850052</v>
+        <v>7.962370784585038</v>
       </c>
       <c r="E136" t="n">
         <v>-6.809857471250713</v>
@@ -37900,7 +37900,7 @@
         <v>45133</v>
       </c>
       <c r="B137" t="n">
-        <v>-10.90377598464469</v>
+        <v>-10.90378613495472</v>
       </c>
       <c r="C137" t="n">
         <v>202.296138737219</v>
@@ -37929,7 +37929,7 @@
         <v>45134</v>
       </c>
       <c r="B138" t="n">
-        <v>-9.657177616546386</v>
+        <v>-9.657187956074065</v>
       </c>
       <c r="C138" t="n">
         <v>199.5115549507713</v>
@@ -37958,7 +37958,7 @@
         <v>45135</v>
       </c>
       <c r="B139" t="n">
-        <v>-9.919121286369348</v>
+        <v>-9.919111051016626</v>
       </c>
       <c r="C139" t="n">
         <v>159.7079792928868</v>
@@ -37990,10 +37990,10 @@
         <v>-7.470227000836516</v>
       </c>
       <c r="C140" t="n">
-        <v>152.6544766202149</v>
+        <v>152.654492729782</v>
       </c>
       <c r="D140" t="n">
-        <v>6.935938907282657</v>
+        <v>6.935945689890133</v>
       </c>
       <c r="E140" t="n">
         <v>-5.313616054516402</v>
@@ -38016,7 +38016,7 @@
         <v>45139</v>
       </c>
       <c r="B141" t="n">
-        <v>-8.327747869080005</v>
+        <v>-8.327758143970243</v>
       </c>
       <c r="C141" t="n">
         <v>161.5188186619657</v>
@@ -38051,7 +38051,7 @@
         <v>168.7345776037631</v>
       </c>
       <c r="D142" t="n">
-        <v>12.03210593210891</v>
+        <v>12.03209849718971</v>
       </c>
       <c r="E142" t="n">
         <v>-5.569118234121451</v>
@@ -38074,13 +38074,13 @@
         <v>45141</v>
       </c>
       <c r="B143" t="n">
-        <v>-6.928046010050426</v>
+        <v>-6.928035510644315</v>
       </c>
       <c r="C143" t="n">
         <v>174.7104058813055</v>
       </c>
       <c r="D143" t="n">
-        <v>20.14490280811663</v>
+        <v>20.14491075062135</v>
       </c>
       <c r="E143" t="n">
         <v>-7.524464252294571</v>
@@ -38103,13 +38103,13 @@
         <v>45142</v>
       </c>
       <c r="B144" t="n">
-        <v>-5.849673602500238</v>
+        <v>-5.849684269824474</v>
       </c>
       <c r="C144" t="n">
         <v>159.8780690899896</v>
       </c>
       <c r="D144" t="n">
-        <v>29.06670727976033</v>
+        <v>29.06671610235676</v>
       </c>
       <c r="E144" t="n">
         <v>-11.95090723691754</v>
@@ -38132,7 +38132,7 @@
         <v>45145</v>
       </c>
       <c r="B145" t="n">
-        <v>-8.349488155767837</v>
+        <v>-8.349498322379745</v>
       </c>
       <c r="C145" t="n">
         <v>132.48411140165</v>
@@ -38161,13 +38161,13 @@
         <v>45146</v>
       </c>
       <c r="B146" t="n">
-        <v>-9.673283202090499</v>
+        <v>-9.673293225680235</v>
       </c>
       <c r="C146" t="n">
-        <v>135.5779718557992</v>
+        <v>135.5779988267238</v>
       </c>
       <c r="D146" t="n">
-        <v>29.72437895039108</v>
+        <v>29.72437048431784</v>
       </c>
       <c r="E146" t="n">
         <v>-15.30300665365612</v>
@@ -38190,7 +38190,7 @@
         <v>45147</v>
       </c>
       <c r="B147" t="n">
-        <v>-10.34052310460761</v>
+        <v>-10.34053304924153</v>
       </c>
       <c r="C147" t="n">
         <v>141.1748940370877</v>
@@ -38222,7 +38222,7 @@
         <v>-11.86883774865826</v>
       </c>
       <c r="C148" t="n">
-        <v>132.9957020468045</v>
+        <v>132.995728345579</v>
       </c>
       <c r="D148" t="n">
         <v>27.91116864153931</v>
@@ -38277,7 +38277,7 @@
         <v>45152</v>
       </c>
       <c r="B150" t="n">
-        <v>-14.84357390140226</v>
+        <v>-14.84358323284842</v>
       </c>
       <c r="C150" t="n">
         <v>151.9457111947966</v>
@@ -38335,13 +38335,13 @@
         <v>45155</v>
       </c>
       <c r="B152" t="n">
-        <v>-14.20933771281898</v>
+        <v>-14.2093281945193</v>
       </c>
       <c r="C152" t="n">
         <v>173.308966021298</v>
       </c>
       <c r="D152" t="n">
-        <v>21.81480286446322</v>
+        <v>21.81479511664144</v>
       </c>
       <c r="E152" t="n">
         <v>-17.48065633488233</v>
@@ -38422,10 +38422,10 @@
         <v>45160</v>
       </c>
       <c r="B155" t="n">
-        <v>-12.42177377359868</v>
+        <v>-12.42178330049941</v>
       </c>
       <c r="C155" t="n">
-        <v>147.9350533313995</v>
+        <v>147.9350272173429</v>
       </c>
       <c r="D155" t="n">
         <v>28.08843931965839</v>
@@ -38454,7 +38454,7 @@
         <v>-13.48412156199127</v>
       </c>
       <c r="C156" t="n">
-        <v>158.0355686785542</v>
+        <v>158.0355408843396</v>
       </c>
       <c r="D156" t="n">
         <v>24.72822037209339</v>
@@ -38483,7 +38483,7 @@
         <v>-13.87669122674596</v>
       </c>
       <c r="C157" t="n">
-        <v>154.5704396392132</v>
+        <v>154.5704117957232</v>
       </c>
       <c r="D157" t="n">
         <v>21.6056490237043</v>
@@ -38509,7 +38509,7 @@
         <v>45163</v>
       </c>
       <c r="B158" t="n">
-        <v>-16.09104790316577</v>
+        <v>-16.09105672223842</v>
       </c>
       <c r="C158" t="n">
         <v>154.2975806466734</v>
@@ -38654,7 +38654,7 @@
         <v>45170</v>
       </c>
       <c r="B163" t="n">
-        <v>-11.55011060542932</v>
+        <v>-11.55012016758056</v>
       </c>
       <c r="C163" t="n">
         <v>158.1326285811827</v>
@@ -38686,7 +38686,7 @@
         <v>-9.588212526902707</v>
       </c>
       <c r="C164" t="n">
-        <v>165.0285393100353</v>
+        <v>165.0285096710109</v>
       </c>
       <c r="D164" t="n">
         <v>28.67010707910678</v>
@@ -38712,10 +38712,10 @@
         <v>45174</v>
       </c>
       <c r="B165" t="n">
-        <v>-8.890428870573853</v>
+        <v>-8.890419081707391</v>
       </c>
       <c r="C165" t="n">
-        <v>135.15564485893</v>
+        <v>135.1556684959676</v>
       </c>
       <c r="D165" t="n">
         <v>24.94943664787912</v>
@@ -38770,7 +38770,7 @@
         <v>45176</v>
       </c>
       <c r="B167" t="n">
-        <v>-10.38720324750275</v>
+        <v>-10.38719357887915</v>
       </c>
       <c r="C167" t="n">
         <v>110.2304853363235</v>
@@ -38857,7 +38857,7 @@
         <v>45181</v>
       </c>
       <c r="B170" t="n">
-        <v>-15.96980420157528</v>
+        <v>-15.96979556986899</v>
       </c>
       <c r="C170" t="n">
         <v>106.3263601890171</v>
@@ -38886,7 +38886,7 @@
         <v>45182</v>
       </c>
       <c r="B171" t="n">
-        <v>-14.35528984158396</v>
+        <v>-14.35528110144222</v>
       </c>
       <c r="C171" t="n">
         <v>95.27136880301103</v>
@@ -38947,7 +38947,7 @@
         <v>-18.53962451495939</v>
       </c>
       <c r="C173" t="n">
-        <v>101.6180558669237</v>
+        <v>101.6180382107684</v>
       </c>
       <c r="D173" t="n">
         <v>12.4834676955101</v>
@@ -38973,7 +38973,7 @@
         <v>45187</v>
       </c>
       <c r="B174" t="n">
-        <v>-21.60490566682807</v>
+        <v>-21.60491319556986</v>
       </c>
       <c r="C174" t="n">
         <v>108.995145875079</v>
@@ -39060,7 +39060,7 @@
         <v>45191</v>
       </c>
       <c r="B177" t="n">
-        <v>-23.85200469695403</v>
+        <v>-23.85201190152254</v>
       </c>
       <c r="C177" t="n">
         <v>163.2386697102644</v>
@@ -39205,7 +39205,7 @@
         <v>45198</v>
       </c>
       <c r="B182" t="n">
-        <v>-18.7381083090693</v>
+        <v>-18.73810024193879</v>
       </c>
       <c r="C182" t="n">
         <v>133.0172406508351</v>
@@ -39321,7 +39321,7 @@
         <v>45205</v>
       </c>
       <c r="B186" t="n">
-        <v>-14.9042523496672</v>
+        <v>-14.90426120607391</v>
       </c>
       <c r="C186" t="n">
         <v>202.0556569992174</v>
@@ -39437,7 +39437,7 @@
         <v>45211</v>
       </c>
       <c r="B190" t="n">
-        <v>-14.35222675424756</v>
+        <v>-14.35223563928886</v>
       </c>
       <c r="C190" t="n">
         <v>179.3184896173734</v>
@@ -39495,7 +39495,7 @@
         <v>45215</v>
       </c>
       <c r="B192" t="n">
-        <v>-13.84521422352966</v>
+        <v>-13.84522320832182</v>
       </c>
       <c r="C192" t="n">
         <v>202.200918102904</v>
@@ -39611,7 +39611,7 @@
         <v>45219</v>
       </c>
       <c r="B196" t="n">
-        <v>-12.05506209322028</v>
+        <v>-12.05505240831574</v>
       </c>
       <c r="C196" t="n">
         <v>201.170088481584</v>
@@ -39669,7 +39669,7 @@
         <v>45224</v>
       </c>
       <c r="B198" t="n">
-        <v>-14.3513035764168</v>
+        <v>-14.35131311214994</v>
       </c>
       <c r="C198" t="n">
         <v>177.6846988203517</v>
@@ -39698,7 +39698,7 @@
         <v>45225</v>
       </c>
       <c r="B199" t="n">
-        <v>-14.9968642604219</v>
+        <v>-14.99685491115055</v>
       </c>
       <c r="C199" t="n">
         <v>178.8858050413006</v>
@@ -39727,7 +39727,7 @@
         <v>45226</v>
       </c>
       <c r="B200" t="n">
-        <v>-17.48594993637738</v>
+        <v>-17.48594102412724</v>
       </c>
       <c r="C200" t="n">
         <v>178.7600986065189</v>
@@ -39843,7 +39843,7 @@
         <v>45232</v>
       </c>
       <c r="B204" t="n">
-        <v>-18.99390981891613</v>
+        <v>-18.9939011656184</v>
       </c>
       <c r="C204" t="n">
         <v>178.811508521793</v>
@@ -39988,7 +39988,7 @@
         <v>45239</v>
       </c>
       <c r="B209" t="n">
-        <v>-24.47623247231878</v>
+        <v>-24.47624007225212</v>
       </c>
       <c r="C209" t="n">
         <v>208.7924474591288</v>
@@ -40046,7 +40046,7 @@
         <v>45243</v>
       </c>
       <c r="B211" t="n">
-        <v>-25.78436669688707</v>
+        <v>-25.78437407622363</v>
       </c>
       <c r="C211" t="n">
         <v>210.62220554906</v>
@@ -40220,7 +40220,7 @@
         <v>45252</v>
       </c>
       <c r="B217" t="n">
-        <v>-26.0009359739691</v>
+        <v>-26.00092855842257</v>
       </c>
       <c r="C217" t="n">
         <v>218.7224781764794</v>
@@ -40452,7 +40452,7 @@
         <v>45265</v>
       </c>
       <c r="B225" t="n">
-        <v>-13.10361860244651</v>
+        <v>-13.10361010636192</v>
       </c>
       <c r="C225" t="n">
         <v>221.0022634926906</v>
@@ -40655,7 +40655,7 @@
         <v>45274</v>
       </c>
       <c r="B232" t="n">
-        <v>-13.82368724957191</v>
+        <v>-13.82369542031192</v>
       </c>
       <c r="C232" t="n">
         <v>185.3729830894533</v>
@@ -40684,7 +40684,7 @@
         <v>45275</v>
       </c>
       <c r="B233" t="n">
-        <v>-15.16835498771169</v>
+        <v>-15.16836298401035</v>
       </c>
       <c r="C233" t="n">
         <v>179.1240120750808</v>
@@ -40713,7 +40713,7 @@
         <v>45278</v>
       </c>
       <c r="B234" t="n">
-        <v>-14.15627242252976</v>
+        <v>-14.1562805196334</v>
       </c>
       <c r="C234" t="n">
         <v>171.3009355407351</v>
@@ -40742,7 +40742,7 @@
         <v>45279</v>
       </c>
       <c r="B235" t="n">
-        <v>-16.21252044165285</v>
+        <v>-16.21251260699229</v>
       </c>
       <c r="C235" t="n">
         <v>174.8890272432232</v>
@@ -40829,7 +40829,7 @@
         <v>45282</v>
       </c>
       <c r="B238" t="n">
-        <v>-20.26453194091654</v>
+        <v>-20.26452446562553</v>
       </c>
       <c r="C238" t="n">
         <v>163.8149586492102</v>
@@ -40887,7 +40887,7 @@
         <v>45287</v>
       </c>
       <c r="B240" t="n">
-        <v>-17.39147860811985</v>
+        <v>-17.39148634395696</v>
       </c>
       <c r="C240" t="n">
         <v>165.5706962360213</v>
@@ -40945,7 +40945,7 @@
         <v>45289</v>
       </c>
       <c r="B242" t="n">
-        <v>-12.53100243390863</v>
+        <v>-12.53099392845242</v>
       </c>
       <c r="C242" t="n">
         <v>169.1061923078513</v>
@@ -40974,7 +40974,7 @@
         <v>45292</v>
       </c>
       <c r="B243" t="n">
-        <v>-10.30125869138323</v>
+        <v>-10.30124987455253</v>
       </c>
       <c r="C243" t="n">
         <v>180.3139278910657</v>
@@ -41003,7 +41003,7 @@
         <v>45293</v>
       </c>
       <c r="B244" t="n">
-        <v>-4.010788269032329</v>
+        <v>-4.010798258973802</v>
       </c>
       <c r="C244" t="n">
         <v>195.2815116358317</v>
@@ -41090,7 +41090,7 @@
         <v>45296</v>
       </c>
       <c r="B247" t="n">
-        <v>-2.678128657889611</v>
+        <v>-2.67813845135938</v>
       </c>
       <c r="C247" t="n">
         <v>180.9280790104141</v>
@@ -41177,7 +41177,7 @@
         <v>45301</v>
       </c>
       <c r="B250" t="n">
-        <v>-4.974648293557626</v>
+        <v>-4.9746579170729</v>
       </c>
       <c r="C250" t="n">
         <v>169.2362350858972</v>
@@ -41235,7 +41235,7 @@
         <v>45303</v>
       </c>
       <c r="B252" t="n">
-        <v>-2.697371328971887</v>
+        <v>-2.697361350287686</v>
       </c>
       <c r="C252" t="n">
         <v>167.9051238982196</v>
@@ -41322,7 +41322,7 @@
         <v>45308</v>
       </c>
       <c r="B255" t="n">
-        <v>-8.16948223785654</v>
+        <v>-8.169491443864418</v>
       </c>
       <c r="C255" t="n">
         <v>152.9905921263437</v>
@@ -41351,7 +41351,7 @@
         <v>45309</v>
       </c>
       <c r="B256" t="n">
-        <v>-6.089699752964862</v>
+        <v>-6.089690160594818</v>
       </c>
       <c r="C256" t="n">
         <v>155.0464666075978</v>
@@ -41409,7 +41409,7 @@
         <v>45314</v>
       </c>
       <c r="B258" t="n">
-        <v>-6.139951758357897</v>
+        <v>-6.139961566785212</v>
       </c>
       <c r="C258" t="n">
         <v>140.8904631423923</v>
@@ -41467,7 +41467,7 @@
         <v>45316</v>
       </c>
       <c r="B260" t="n">
-        <v>5.033166146726265</v>
+        <v>5.033177136696332</v>
       </c>
       <c r="C260" t="n">
         <v>145.073041225326</v>
@@ -41699,7 +41699,7 @@
         <v>45329</v>
       </c>
       <c r="B268" t="n">
-        <v>33.97244284667431</v>
+        <v>33.97243404176398</v>
       </c>
       <c r="C268" t="n">
         <v>181.7043941628539</v>
@@ -41728,7 +41728,7 @@
         <v>45330</v>
       </c>
       <c r="B269" t="n">
-        <v>32.53545655831574</v>
+        <v>32.53546515716834</v>
       </c>
       <c r="C269" t="n">
         <v>156.1297972346655</v>
@@ -41815,7 +41815,7 @@
         <v>45335</v>
       </c>
       <c r="B272" t="n">
-        <v>42.72661616214479</v>
+        <v>42.72662573853441</v>
       </c>
       <c r="C272" t="n">
         <v>149.1226168467065</v>
@@ -41902,7 +41902,7 @@
         <v>45338</v>
       </c>
       <c r="B275" t="n">
-        <v>37.12264153573543</v>
+        <v>37.12263304035834</v>
       </c>
       <c r="C275" t="n">
         <v>129.837453986798</v>
@@ -41931,7 +41931,7 @@
         <v>45341</v>
       </c>
       <c r="B276" t="n">
-        <v>35.99184904560651</v>
+        <v>35.9918405336326</v>
       </c>
       <c r="C276" t="n">
         <v>144.7472317469186</v>
@@ -41960,7 +41960,7 @@
         <v>45342</v>
       </c>
       <c r="B277" t="n">
-        <v>40.94061702583809</v>
+        <v>40.9406079382163</v>
       </c>
       <c r="C277" t="n">
         <v>141.5522191096715</v>
@@ -41989,7 +41989,7 @@
         <v>45343</v>
       </c>
       <c r="B278" t="n">
-        <v>42.54254935578106</v>
+        <v>42.54253999086652</v>
       </c>
       <c r="C278" t="n">
         <v>137.5795700585137</v>
@@ -42018,7 +42018,7 @@
         <v>45344</v>
       </c>
       <c r="B279" t="n">
-        <v>47.75462322516528</v>
+        <v>47.75461321299499</v>
       </c>
       <c r="C279" t="n">
         <v>144.808011079152</v>
@@ -42163,7 +42163,7 @@
         <v>45351</v>
       </c>
       <c r="B284" t="n">
-        <v>42.80002518007056</v>
+        <v>42.80003471271887</v>
       </c>
       <c r="C284" t="n">
         <v>127.5487402573614</v>
@@ -42337,7 +42337,7 @@
         <v>45362</v>
       </c>
       <c r="B290" t="n">
-        <v>53.34025765526022</v>
+        <v>53.34024671586983</v>
       </c>
       <c r="C290" t="n">
         <v>136.0374315805776</v>
@@ -42453,7 +42453,7 @@
         <v>45366</v>
       </c>
       <c r="B294" t="n">
-        <v>34.83403301905687</v>
+        <v>34.83404194684776</v>
       </c>
       <c r="C294" t="n">
         <v>114.8707470876117</v>
@@ -42482,7 +42482,7 @@
         <v>45369</v>
       </c>
       <c r="B295" t="n">
-        <v>30.08323091221332</v>
+        <v>30.0832223934989</v>
       </c>
       <c r="C295" t="n">
         <v>102.3148403760358</v>
@@ -42511,7 +42511,7 @@
         <v>45370</v>
       </c>
       <c r="B296" t="n">
-        <v>29.86802525644414</v>
+        <v>29.86801663111855</v>
       </c>
       <c r="C296" t="n">
         <v>104.2035975792168</v>
@@ -42569,7 +42569,7 @@
         <v>45372</v>
       </c>
       <c r="B298" t="n">
-        <v>38.49186576181005</v>
+        <v>38.49187542811692</v>
       </c>
       <c r="C298" t="n">
         <v>108.5391886302269</v>
@@ -42685,7 +42685,7 @@
         <v>45379</v>
       </c>
       <c r="B302" t="n">
-        <v>44.73105973661957</v>
+        <v>44.73104940365835</v>
       </c>
       <c r="C302" t="n">
         <v>95.01424171337425</v>
@@ -42830,7 +42830,7 @@
         <v>45387</v>
       </c>
       <c r="B307" t="n">
-        <v>52.1740336800861</v>
+        <v>52.1740226269858</v>
       </c>
       <c r="C307" t="n">
         <v>151.132003276984</v>
@@ -42888,7 +42888,7 @@
         <v>45391</v>
       </c>
       <c r="B309" t="n">
-        <v>57.20392840578963</v>
+        <v>57.2039163725407</v>
       </c>
       <c r="C309" t="n">
         <v>176.0565668438081</v>
@@ -43004,7 +43004,7 @@
         <v>45398</v>
       </c>
       <c r="B313" t="n">
-        <v>45.45014342621376</v>
+        <v>45.45013278076082</v>
       </c>
       <c r="C313" t="n">
         <v>133.8561616158762</v>
@@ -43033,7 +43033,7 @@
         <v>45400</v>
       </c>
       <c r="B314" t="n">
-        <v>41.60742444180878</v>
+        <v>41.60741422319869</v>
       </c>
       <c r="C314" t="n">
         <v>127.8424724555976</v>
@@ -43091,7 +43091,7 @@
         <v>45404</v>
       </c>
       <c r="B316" t="n">
-        <v>39.04832957155872</v>
+        <v>39.04833945880928</v>
       </c>
       <c r="C316" t="n">
         <v>134.3063775493436</v>
@@ -43149,7 +43149,7 @@
         <v>45406</v>
       </c>
       <c r="B318" t="n">
-        <v>45.36822677029662</v>
+        <v>45.3682369306164</v>
       </c>
       <c r="C318" t="n">
         <v>126.6181902269033</v>
@@ -43236,7 +43236,7 @@
         <v>45411</v>
       </c>
       <c r="B321" t="n">
-        <v>45.10362949896689</v>
+        <v>45.10363974659954</v>
       </c>
       <c r="C321" t="n">
         <v>110.7439339286821</v>
@@ -43265,7 +43265,7 @@
         <v>45412</v>
       </c>
       <c r="B322" t="n">
-        <v>46.40877317780343</v>
+        <v>46.40878358423728</v>
       </c>
       <c r="C322" t="n">
         <v>111.8983328016571</v>
@@ -43294,7 +43294,7 @@
         <v>45414</v>
       </c>
       <c r="B323" t="n">
-        <v>47.98852405566016</v>
+        <v>47.98851341356609</v>
       </c>
       <c r="C323" t="n">
         <v>111.377603133298</v>
@@ -43323,7 +43323,7 @@
         <v>45415</v>
       </c>
       <c r="B324" t="n">
-        <v>46.67678265656121</v>
+        <v>46.67677221034363</v>
       </c>
       <c r="C324" t="n">
         <v>98.17210326323145</v>
@@ -43352,7 +43352,7 @@
         <v>45418</v>
       </c>
       <c r="B325" t="n">
-        <v>44.12433254016144</v>
+        <v>44.12434279572761</v>
       </c>
       <c r="C325" t="n">
         <v>87.09032135601906</v>
@@ -43526,7 +43526,7 @@
         <v>45426</v>
       </c>
       <c r="B331" t="n">
-        <v>40.18467365477845</v>
+        <v>40.18468345973459</v>
       </c>
       <c r="C331" t="n">
         <v>67.77069653881185</v>
@@ -43584,7 +43584,7 @@
         <v>45428</v>
       </c>
       <c r="B333" t="n">
-        <v>41.44271522537404</v>
+        <v>41.44270533438712</v>
       </c>
       <c r="C333" t="n">
         <v>31.96061295663837</v>
@@ -43613,7 +43613,7 @@
         <v>45429</v>
       </c>
       <c r="B334" t="n">
-        <v>44.08176246239029</v>
+        <v>44.08175234476359</v>
       </c>
       <c r="C334" t="n">
         <v>23.13787803174869</v>
@@ -43903,7 +43903,7 @@
         <v>45446</v>
       </c>
       <c r="B344" t="n">
-        <v>48.2042465851926</v>
+        <v>48.20423652213213</v>
       </c>
       <c r="C344" t="n">
         <v>11.90182110091218</v>
@@ -43961,7 +43961,7 @@
         <v>45448</v>
       </c>
       <c r="B346" t="n">
-        <v>35.75153184663171</v>
+        <v>35.75154127824381</v>
       </c>
       <c r="C346" t="n">
         <v>11.29012292779539</v>
@@ -44019,7 +44019,7 @@
         <v>45450</v>
       </c>
       <c r="B348" t="n">
-        <v>39.98350681152986</v>
+        <v>39.98349717396849</v>
       </c>
       <c r="C348" t="n">
         <v>22.74986696523871</v>
@@ -44193,7 +44193,7 @@
         <v>45461</v>
       </c>
       <c r="B354" t="n">
-        <v>44.00424335818942</v>
+        <v>44.00425294196648</v>
       </c>
       <c r="C354" t="n">
         <v>18.18136724781729</v>
@@ -44222,7 +44222,7 @@
         <v>45462</v>
       </c>
       <c r="B355" t="n">
-        <v>42.70059571670006</v>
+        <v>42.70060523705279</v>
       </c>
       <c r="C355" t="n">
         <v>18.11693565584838</v>
@@ -44280,7 +44280,7 @@
         <v>45464</v>
       </c>
       <c r="B357" t="n">
-        <v>42.10298548188219</v>
+        <v>42.10297592683827</v>
       </c>
       <c r="C357" t="n">
         <v>23.53684064747041</v>
@@ -44309,7 +44309,7 @@
         <v>45467</v>
       </c>
       <c r="B358" t="n">
-        <v>41.89946671705363</v>
+        <v>41.89945718218131</v>
       </c>
       <c r="C358" t="n">
         <v>24.02309793363384</v>
@@ -44425,7 +44425,7 @@
         <v>45471</v>
       </c>
       <c r="B362" t="n">
-        <v>42.28021472067896</v>
+        <v>42.28022419405666</v>
       </c>
       <c r="C362" t="n">
         <v>17.71554803559778</v>
@@ -44483,7 +44483,7 @@
         <v>45475</v>
       </c>
       <c r="B364" t="n">
-        <v>52.01610987274086</v>
+        <v>52.01612008934278</v>
       </c>
       <c r="C364" t="n">
         <v>32.10992860845121</v>
@@ -44541,7 +44541,7 @@
         <v>45477</v>
       </c>
       <c r="B366" t="n">
-        <v>49.97883944096198</v>
+        <v>49.97882932578788</v>
       </c>
       <c r="C366" t="n">
         <v>48.31607086128565</v>
@@ -44628,7 +44628,7 @@
         <v>45482</v>
       </c>
       <c r="B369" t="n">
-        <v>51.35977167856935</v>
+        <v>51.35976122398402</v>
       </c>
       <c r="C369" t="n">
         <v>54.36188215539068</v>
@@ -44657,7 +44657,7 @@
         <v>45483</v>
       </c>
       <c r="B370" t="n">
-        <v>47.55479536888721</v>
+        <v>47.5548054271006</v>
       </c>
       <c r="C370" t="n">
         <v>49.50744875439488</v>
@@ -44686,7 +44686,7 @@
         <v>45484</v>
       </c>
       <c r="B371" t="n">
-        <v>48.075745207686</v>
+        <v>48.07575529389776</v>
       </c>
       <c r="C371" t="n">
         <v>53.78465182312586</v>
@@ -44715,7 +44715,7 @@
         <v>45485</v>
       </c>
       <c r="B372" t="n">
-        <v>48.35205575469506</v>
+        <v>48.35204571278184</v>
       </c>
       <c r="C372" t="n">
         <v>52.26790894618509</v>
@@ -44773,7 +44773,7 @@
         <v>45489</v>
       </c>
       <c r="B374" t="n">
-        <v>50.34657239732812</v>
+        <v>50.34656219637304</v>
       </c>
       <c r="C374" t="n">
         <v>49.08622027227223</v>
@@ -44802,7 +44802,7 @@
         <v>45491</v>
       </c>
       <c r="B375" t="n">
-        <v>48.75576838752951</v>
+        <v>48.75577848304522</v>
       </c>
       <c r="C375" t="n">
         <v>42.84370609323616</v>
